--- a/data/previous.xlsx
+++ b/data/previous.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{84C4A5A4-774F-413D-BA65-C4BA17ABD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2094F5CC-F837-4616-832E-52D34E254F01}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7DD92-A4EA-4BAD-BF0F-6288B1C0BB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資金移動" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資金移動!$A$4:$K$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">資金移動!$A$1:$K$90</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">資金移動!$A$1:$K$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">資金移動!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="429">
   <si>
     <t>登録番号</t>
     <rPh sb="0" eb="2">
@@ -2657,9 +2657,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>03-4530-0365</t>
-  </si>
-  <si>
     <t>東京都港区港南２－１６－５</t>
     <rPh sb="0" eb="3">
       <t>トウキョウト</t>
@@ -2860,26 +2857,6 @@
   </si>
   <si>
     <t>Ｒｅｍｉｔｌｙ　Ｊａｐａｎ　株式会社</t>
-  </si>
-  <si>
-    <t>166-0011</t>
-  </si>
-  <si>
-    <t>東京都杉並区梅里２－９－１３
-ライオンズマンション高円寺５０１</t>
-    <rPh sb="0" eb="3">
-      <t>トウキョウト</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>スギナミク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ウメサト</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>コウエンジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>103-0027</t>
@@ -3643,6 +3620,39 @@
       <t>キタアオヤマ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>東京都港区赤坂３－２１－１２
+陶香堂ビル５階</t>
+    <rPh sb="0" eb="3">
+      <t>トウキョウト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミナトク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>アカサカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>関東財務局長
+第00103号</t>
+  </si>
+  <si>
+    <t>インタセクト・コミュニケーションズ株式会社</t>
+  </si>
+  <si>
+    <t>101-0052</t>
+  </si>
+  <si>
+    <t>東京都千代田区神田小川町３－１</t>
+  </si>
+  <si>
+    <t>03-3233-3523</t>
+  </si>
+  <si>
+    <t>03-6694-4276</t>
   </si>
 </sst>
 </file>
@@ -4674,6 +4684,60 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4689,6 +4753,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4704,6 +4774,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4713,18 +4789,45 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="58" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4740,6 +4843,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4752,17 +4858,32 @@
     <xf numFmtId="179" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4773,119 +4894,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5292,16 +5302,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.7265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43" style="42" customWidth="1"/>
-    <col min="5" max="5" width="15.7265625" style="42" customWidth="1"/>
+    <col min="4" max="4" width="43" style="79" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="79" customWidth="1"/>
     <col min="6" max="6" width="12.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.90625" style="42" customWidth="1"/>
+    <col min="7" max="7" width="39.90625" style="79" customWidth="1"/>
     <col min="8" max="8" width="16.7265625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -5335,10 +5345,10 @@
     </row>
     <row r="3" spans="1:11" s="9" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="str">
-        <f>"【全業者数："&amp;COUNTA($B$5:$B$860)&amp;"】"</f>
-        <v>【全業者数：84】</v>
-      </c>
-      <c r="B3" s="43"/>
+        <f>"【全業者数："&amp;COUNTA($B$5:$B$861)&amp;"】"</f>
+        <v>【全業者数：85】</v>
+      </c>
+      <c r="B3" s="10"/>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -5346,7 +5356,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
       <c r="I3" s="93">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="J3" s="93"/>
       <c r="K3" s="93"/>
@@ -5397,2519 +5407,2548 @@
       <c r="J5" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="K5" s="53" t="s">
+      <c r="K5" s="11" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="54" t="str">
-        <f>"北海道財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"北海道財務局*")&amp;"業者】"</f>
+      <c r="A6" s="12" t="str">
+        <f>"北海道財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"北海道財務局*")&amp;"業者】"</f>
         <v>北海道財務局
 【計2業者】</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="14">
+        <v>44592</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="E6" s="16">
+        <v>5010001125807</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="K6" s="19"/>
+    </row>
+    <row r="7" spans="1:11" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C7" s="22">
+        <v>45833</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="E7" s="24">
+        <v>9010401124520</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="K7" s="26"/>
+    </row>
+    <row r="8" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="27" t="str">
+        <f>"関東財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"関東財務局*")&amp;"業者】"</f>
+        <v>関東財務局
+【計78業者】</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="29">
+        <v>40269</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="31">
+        <v>3010401058641</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" s="33"/>
+    </row>
+    <row r="9" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="34"/>
+      <c r="B9" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="36">
+        <v>40340</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="38">
+        <v>3010701023295</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>387</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K9" s="40"/>
+    </row>
+    <row r="10" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="41"/>
+      <c r="B10" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="36">
+        <v>40389</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="E10" s="38">
+        <v>5010401089313</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K10" s="40"/>
+    </row>
+    <row r="11" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="41"/>
+      <c r="B11" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="36">
+        <v>40497</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="E11" s="38">
+        <v>5010501030903</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K11" s="40"/>
+    </row>
+    <row r="12" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="41"/>
+      <c r="B12" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="36">
+        <v>40519</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="38">
+        <v>9010401089532</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K12" s="40"/>
+    </row>
+    <row r="13" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="41"/>
+      <c r="B13" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="36">
+        <v>40603</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="E13" s="38">
+        <v>6010401071583</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>331</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K13" s="40"/>
+    </row>
+    <row r="14" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="41"/>
+      <c r="B14" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="36">
+        <v>40644</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" s="38">
+        <v>9010001134572</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K14" s="40"/>
+    </row>
+    <row r="15" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="41"/>
+      <c r="B15" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="36">
+        <v>40681</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="38">
+        <v>1010001067912</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K15" s="40"/>
+    </row>
+    <row r="16" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="41"/>
+      <c r="B16" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="36">
+        <v>40715</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="38">
+        <v>8010001103611</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="H16" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K16" s="40"/>
+    </row>
+    <row r="17" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="41"/>
+      <c r="B17" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="36">
+        <v>40750</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="E17" s="38">
+        <v>5010601030547</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K17" s="40"/>
+    </row>
+    <row r="18" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="41"/>
+      <c r="B18" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="36">
+        <v>40798</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="E18" s="38">
+        <v>4010401058731</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="H18" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K18" s="40"/>
+    </row>
+    <row r="19" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="41"/>
+      <c r="B19" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="36">
+        <v>40863</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" s="38">
+        <v>7011101036066</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="H19" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="J19" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K19" s="40"/>
+    </row>
+    <row r="20" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="41"/>
+      <c r="B20" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="36">
+        <v>40954</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="38">
+        <v>1011101057035</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K20" s="40"/>
+    </row>
+    <row r="21" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="41"/>
+      <c r="B21" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="36">
+        <v>40966</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21" s="38">
+        <v>4010401084380</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K21" s="40"/>
+    </row>
+    <row r="22" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="41"/>
+      <c r="B22" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="36">
+        <v>40996</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="E22" s="38">
+        <v>1010401095934</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="H22" s="43" t="s">
+        <v>405</v>
+      </c>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K22" s="40"/>
+    </row>
+    <row r="23" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="41"/>
+      <c r="B23" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="36">
+        <v>41085</v>
+      </c>
+      <c r="D23" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="E23" s="38">
+        <v>6011101062006</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K23" s="40"/>
+    </row>
+    <row r="24" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="41"/>
+      <c r="B24" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="36">
+        <v>41122</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24" s="38">
+        <v>3700150006491</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K24" s="40"/>
+    </row>
+    <row r="25" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="41"/>
+      <c r="B25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="36">
+        <v>41264</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25" s="38">
+        <v>2010401087071</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="G25" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K25" s="40"/>
+    </row>
+    <row r="26" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="41"/>
+      <c r="B26" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="44">
+        <v>41442</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="E26" s="38">
+        <v>6010401094452</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>422</v>
+      </c>
+      <c r="H26" s="43" t="s">
+        <v>413</v>
+      </c>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K26" s="40"/>
+    </row>
+    <row r="27" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="41"/>
+      <c r="B27" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="44">
+        <v>41451</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="E27" s="38">
+        <v>9010401099531</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="H27" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K27" s="40"/>
+    </row>
+    <row r="28" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="41"/>
+      <c r="B28" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="44">
+        <v>41516</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="E28" s="38">
+        <v>6011101063994</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K28" s="40"/>
+    </row>
+    <row r="29" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="41"/>
+      <c r="B29" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="44">
+        <v>41558</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="38">
+        <v>1020001100705</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K29" s="40"/>
+    </row>
+    <row r="30" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="41"/>
+      <c r="B30" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="44">
+        <v>41880</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="E30" s="38">
+        <v>9010401105000</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K30" s="40"/>
+    </row>
+    <row r="31" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="41"/>
+      <c r="B31" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="44">
+        <v>41969</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="E31" s="38">
+        <v>6011001005411</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K31" s="40"/>
+    </row>
+    <row r="32" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="41"/>
+      <c r="B32" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="44">
+        <v>42041</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="E32" s="38">
+        <v>6011001092945</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="G32" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="H32" s="43" t="s">
+        <v>334</v>
+      </c>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K32" s="40"/>
+    </row>
+    <row r="33" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="45"/>
+      <c r="B33" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="44">
+        <v>42234</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="E33" s="38">
+        <v>5010401114302</v>
+      </c>
+      <c r="F33" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="G33" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K33" s="40"/>
+    </row>
+    <row r="34" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="45"/>
+      <c r="B34" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="44">
+        <v>42234</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="E34" s="38">
+        <v>4011001100453</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="G34" s="42" t="s">
+        <v>328</v>
+      </c>
+      <c r="H34" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K34" s="40"/>
+    </row>
+    <row r="35" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="45"/>
+      <c r="B35" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="44">
+        <v>42340</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="E35" s="38">
+        <v>9010401113770</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="G35" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" s="40"/>
+    </row>
+    <row r="36" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="45"/>
+      <c r="B36" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="44">
+        <v>42481</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="E36" s="38">
+        <v>1011001053935</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="H36" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K36" s="40"/>
+    </row>
+    <row r="37" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="46"/>
+      <c r="B37" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="44">
+        <v>42506</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="E37" s="38">
+        <v>8010001164001</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="G37" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K37" s="40"/>
+    </row>
+    <row r="38" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="45"/>
+      <c r="B38" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="47">
+        <v>42544</v>
+      </c>
+      <c r="D38" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="E38" s="38">
+        <v>4010001166406</v>
+      </c>
+      <c r="F38" s="43" t="s">
+        <v>399</v>
+      </c>
+      <c r="G38" s="42" t="s">
+        <v>400</v>
+      </c>
+      <c r="H38" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K38" s="40"/>
+    </row>
+    <row r="39" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="41"/>
+      <c r="B39" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="47">
+        <v>42704</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="E39" s="38">
+        <v>7700150006587</v>
+      </c>
+      <c r="F39" s="43" t="s">
+        <v>324</v>
+      </c>
+      <c r="G39" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="H39" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K39" s="40"/>
+    </row>
+    <row r="40" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="41"/>
+      <c r="B40" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="47">
+        <v>42830</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="E40" s="38">
+        <v>9011101071185</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="G40" s="42" t="s">
+        <v>350</v>
+      </c>
+      <c r="H40" s="43" t="s">
+        <v>351</v>
+      </c>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K40" s="40"/>
+    </row>
+    <row r="41" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="41"/>
+      <c r="B41" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="47">
+        <v>42919</v>
+      </c>
+      <c r="D41" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="E41" s="38">
+        <v>2010001057425</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="G41" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="H41" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K41" s="40"/>
+    </row>
+    <row r="42" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="41"/>
+      <c r="B42" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="47">
+        <v>43013</v>
+      </c>
+      <c r="D42" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="E42" s="38">
+        <v>6011101080437</v>
+      </c>
+      <c r="F42" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G42" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="H42" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K42" s="40"/>
+    </row>
+    <row r="43" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="41"/>
+      <c r="B43" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="47">
+        <v>43060</v>
+      </c>
+      <c r="D43" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="E43" s="38">
+        <v>1011101032839</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="G43" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="H43" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K43" s="40"/>
+    </row>
+    <row r="44" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="41"/>
+      <c r="B44" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="47">
+        <v>43067</v>
+      </c>
+      <c r="D44" s="42" t="s">
+        <v>414</v>
+      </c>
+      <c r="E44" s="38">
+        <v>5010401069983</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>415</v>
+      </c>
+      <c r="G44" s="42" t="s">
+        <v>416</v>
+      </c>
+      <c r="H44" s="43" t="s">
+        <v>417</v>
+      </c>
+      <c r="I44" s="39"/>
+      <c r="J44" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K44" s="40"/>
+    </row>
+    <row r="45" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="41"/>
+      <c r="B45" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="47">
+        <v>43076</v>
+      </c>
+      <c r="D45" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="E45" s="38">
+        <v>2010001183865</v>
+      </c>
+      <c r="F45" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="G45" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="H45" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K45" s="40"/>
+    </row>
+    <row r="46" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="41"/>
+      <c r="B46" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="47">
+        <v>43117</v>
+      </c>
+      <c r="D46" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="E46" s="38">
+        <v>3011101071892</v>
+      </c>
+      <c r="F46" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" s="42" t="s">
+        <v>345</v>
+      </c>
+      <c r="H46" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="I46" s="39"/>
+      <c r="J46" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K46" s="40"/>
+    </row>
+    <row r="47" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="41"/>
+      <c r="B47" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="47">
+        <v>43173</v>
+      </c>
+      <c r="D47" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="E47" s="38">
+        <v>8010601051334</v>
+      </c>
+      <c r="F47" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="G47" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="H47" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="I47" s="39"/>
+      <c r="J47" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K47" s="40"/>
+    </row>
+    <row r="48" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="41"/>
+      <c r="B48" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="47">
+        <v>43181</v>
+      </c>
+      <c r="D48" s="42" t="s">
+        <v>290</v>
+      </c>
+      <c r="E48" s="38">
+        <v>1010401135178</v>
+      </c>
+      <c r="F48" s="43" t="s">
+        <v>363</v>
+      </c>
+      <c r="G48" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="I48" s="39"/>
+      <c r="J48" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K48" s="40"/>
+    </row>
+    <row r="49" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="41"/>
+      <c r="B49" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="47">
+        <v>43213</v>
+      </c>
+      <c r="D49" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="E49" s="38">
+        <v>1010001188907</v>
+      </c>
+      <c r="F49" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K49" s="40"/>
+    </row>
+    <row r="50" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="41"/>
+      <c r="B50" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="47">
+        <v>43263</v>
+      </c>
+      <c r="D50" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="E50" s="38">
+        <v>3010001183897</v>
+      </c>
+      <c r="F50" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="G50" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="H50" s="43" t="s">
+        <v>418</v>
+      </c>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K50" s="40"/>
+    </row>
+    <row r="51" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="41"/>
+      <c r="B51" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51" s="47">
+        <v>43307</v>
+      </c>
+      <c r="D51" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="E51" s="38">
+        <v>8010001188396</v>
+      </c>
+      <c r="F51" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="G51" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="H51" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="I51" s="39"/>
+      <c r="J51" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K51" s="40"/>
+    </row>
+    <row r="52" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="41"/>
+      <c r="B52" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" s="47">
+        <v>43308</v>
+      </c>
+      <c r="D52" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="38">
+        <v>5011401019978</v>
+      </c>
+      <c r="F52" s="43" t="s">
+        <v>381</v>
+      </c>
+      <c r="G52" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="H52" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K52" s="40"/>
+    </row>
+    <row r="53" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="41"/>
+      <c r="B53" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="47">
+        <v>43327</v>
+      </c>
+      <c r="D53" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="E53" s="38">
+        <v>4010701034738</v>
+      </c>
+      <c r="F53" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="G53" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="H53" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="I53" s="39"/>
+      <c r="J53" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K53" s="40"/>
+    </row>
+    <row r="54" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="41"/>
+      <c r="B54" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="47">
+        <v>43375</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="E54" s="48">
+        <v>4011001117670</v>
+      </c>
+      <c r="F54" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="G54" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="I54" s="39"/>
+      <c r="J54" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K54" s="40"/>
+    </row>
+    <row r="55" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="41"/>
+      <c r="B55" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D55" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="E55" s="48">
+        <v>3013301041741</v>
+      </c>
+      <c r="F55" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G55" s="42" t="s">
+        <v>375</v>
+      </c>
+      <c r="H55" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="I55" s="39"/>
+      <c r="J55" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K55" s="40"/>
+    </row>
+    <row r="56" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="41"/>
+      <c r="B56" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="E56" s="48">
+        <v>3010901038102</v>
+      </c>
+      <c r="F56" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="G56" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="H56" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K56" s="40"/>
+    </row>
+    <row r="57" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="41"/>
+      <c r="B57" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="D57" s="42" t="s">
+        <v>297</v>
+      </c>
+      <c r="E57" s="48">
+        <v>5010001192707</v>
+      </c>
+      <c r="F57" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="G57" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="I57" s="39"/>
+      <c r="J57" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K57" s="40"/>
+    </row>
+    <row r="58" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="41"/>
+      <c r="B58" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="E58" s="48">
+        <v>7013301041449</v>
+      </c>
+      <c r="F58" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="G58" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K58" s="40"/>
+    </row>
+    <row r="59" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="41"/>
+      <c r="B59" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="E59" s="48">
+        <v>3010001167611</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="G59" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="H59" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="I59" s="39"/>
+      <c r="J59" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K59" s="40"/>
+    </row>
+    <row r="60" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="41"/>
+      <c r="B60" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="E60" s="48">
+        <v>3010401049814</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="G60" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="H60" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K60" s="40"/>
+    </row>
+    <row r="61" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="41"/>
+      <c r="B61" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="E61" s="48">
+        <v>2010001190192</v>
+      </c>
+      <c r="F61" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="G61" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="H61" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="I61" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="J61" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K61" s="40"/>
+    </row>
+    <row r="62" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="41"/>
+      <c r="B62" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="47">
+        <v>43868</v>
+      </c>
+      <c r="D62" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="E62" s="48">
+        <v>5011801019594</v>
+      </c>
+      <c r="F62" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="G62" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="H62" s="43" t="s">
+        <v>395</v>
+      </c>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K62" s="40"/>
+    </row>
+    <row r="63" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="41"/>
+      <c r="B63" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="47">
+        <v>43868</v>
+      </c>
+      <c r="D63" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="E63" s="48">
+        <v>3010001161300</v>
+      </c>
+      <c r="F63" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="H63" s="43" t="s">
+        <v>406</v>
+      </c>
+      <c r="I63" s="39"/>
+      <c r="J63" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K63" s="40"/>
+    </row>
+    <row r="64" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="41"/>
+      <c r="B64" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="47">
+        <v>43887</v>
+      </c>
+      <c r="D64" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E64" s="48">
+        <v>9011401020230</v>
+      </c>
+      <c r="F64" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="G64" s="42" t="s">
         <v>343</v>
       </c>
-      <c r="C6" s="45">
-        <v>44592</v>
-      </c>
-      <c r="D6" s="46" t="s">
+      <c r="H64" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="I64" s="39"/>
+      <c r="J64" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K64" s="40"/>
+    </row>
+    <row r="65" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="41"/>
+      <c r="B65" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="47">
+        <v>43888</v>
+      </c>
+      <c r="D65" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="E65" s="48">
+        <v>9010401134148</v>
+      </c>
+      <c r="F65" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="G65" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="H65" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K65" s="40"/>
+    </row>
+    <row r="66" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="41"/>
+      <c r="B66" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C66" s="47">
+        <v>43899</v>
+      </c>
+      <c r="D66" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="E66" s="48">
+        <v>7040001086061</v>
+      </c>
+      <c r="F66" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="G66" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="H66" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K66" s="40"/>
+    </row>
+    <row r="67" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="41"/>
+      <c r="B67" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" s="47">
+        <v>43922</v>
+      </c>
+      <c r="D67" s="42" t="s">
+        <v>304</v>
+      </c>
+      <c r="E67" s="48">
+        <v>6020001125152</v>
+      </c>
+      <c r="F67" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="G67" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="H67" s="43" t="s">
         <v>344</v>
       </c>
-      <c r="E6" s="47">
-        <v>5010001125807</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>214</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>216</v>
-      </c>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49" t="s">
+      <c r="I67" s="39"/>
+      <c r="J67" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="K6" s="55"/>
-    </row>
-    <row r="7" spans="1:11" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56"/>
-      <c r="B7" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="C7" s="50">
-        <v>45833</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="E7" s="52">
-        <v>9010401124520</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>375</v>
-      </c>
-      <c r="G7" s="51" t="s">
+      <c r="K67" s="40"/>
+    </row>
+    <row r="68" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="41"/>
+      <c r="B68" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="C68" s="47">
+        <v>44056</v>
+      </c>
+      <c r="D68" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="E68" s="48">
+        <v>7010001206332</v>
+      </c>
+      <c r="F68" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="G68" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="H68" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="I68" s="39"/>
+      <c r="J68" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K68" s="40"/>
+    </row>
+    <row r="69" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="41"/>
+      <c r="B69" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="47">
+        <v>44070</v>
+      </c>
+      <c r="D69" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="E69" s="48">
+        <v>9011001103831</v>
+      </c>
+      <c r="F69" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="G69" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="H69" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="I69" s="39"/>
+      <c r="J69" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K69" s="40"/>
+    </row>
+    <row r="70" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="41"/>
+      <c r="B70" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="47">
+        <v>44127</v>
+      </c>
+      <c r="D70" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="E70" s="48">
+        <v>8011001127534</v>
+      </c>
+      <c r="F70" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="G70" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="H70" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="I70" s="39"/>
+      <c r="J70" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K70" s="40"/>
+    </row>
+    <row r="71" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="41"/>
+      <c r="B71" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" s="47">
+        <v>44335</v>
+      </c>
+      <c r="D71" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="E71" s="48">
+        <v>6013201011825</v>
+      </c>
+      <c r="F71" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="G71" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="H71" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="I71" s="39"/>
+      <c r="J71" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K71" s="40"/>
+    </row>
+    <row r="72" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="41"/>
+      <c r="B72" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="C72" s="47">
+        <v>44371</v>
+      </c>
+      <c r="D72" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="E72" s="48">
+        <v>8010401050511</v>
+      </c>
+      <c r="F72" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="G72" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="H72" s="43" t="s">
+        <v>403</v>
+      </c>
+      <c r="I72" s="39"/>
+      <c r="J72" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K72" s="40"/>
+    </row>
+    <row r="73" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="41"/>
+      <c r="B73" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C73" s="47">
+        <v>44403</v>
+      </c>
+      <c r="D73" s="42" t="s">
+        <v>310</v>
+      </c>
+      <c r="E73" s="48">
+        <v>5010401134795</v>
+      </c>
+      <c r="F73" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="G73" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="H73" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="I73" s="39"/>
+      <c r="J73" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K73" s="40"/>
+    </row>
+    <row r="74" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="41"/>
+      <c r="B74" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="C74" s="47">
+        <v>44650</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="E74" s="48">
+        <v>5012401017708</v>
+      </c>
+      <c r="F74" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="G74" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="H74" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="I74" s="39"/>
+      <c r="J74" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K74" s="40"/>
+    </row>
+    <row r="75" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="41"/>
+      <c r="B75" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="C75" s="47">
+        <v>44650</v>
+      </c>
+      <c r="D75" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E75" s="48">
+        <v>2040001094812</v>
+      </c>
+      <c r="F75" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="G75" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="H75" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K75" s="40"/>
+    </row>
+    <row r="76" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="41"/>
+      <c r="B76" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C76" s="47">
+        <v>44650</v>
+      </c>
+      <c r="D76" s="42" t="s">
+        <v>312</v>
+      </c>
+      <c r="E76" s="48">
+        <v>8013301009057</v>
+      </c>
+      <c r="F76" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="G76" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="H76" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="I76" s="39"/>
+      <c r="J76" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K76" s="40"/>
+    </row>
+    <row r="77" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="41"/>
+      <c r="B77" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" s="47">
+        <v>44978</v>
+      </c>
+      <c r="D77" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="E77" s="48">
+        <v>4010401049813</v>
+      </c>
+      <c r="F77" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="G77" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="I77" s="39"/>
+      <c r="J77" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K77" s="40"/>
+    </row>
+    <row r="78" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="49"/>
+      <c r="B78" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="C78" s="47">
+        <v>45254</v>
+      </c>
+      <c r="D78" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="E78" s="48">
+        <v>3010401113537</v>
+      </c>
+      <c r="F78" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G78" s="42" t="s">
+        <v>330</v>
+      </c>
+      <c r="H78" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="I78" s="39"/>
+      <c r="J78" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K78" s="40"/>
+    </row>
+    <row r="79" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="49"/>
+      <c r="B79" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="C79" s="47">
+        <v>45275</v>
+      </c>
+      <c r="D79" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="E79" s="48">
+        <v>6011101086450</v>
+      </c>
+      <c r="F79" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="G79" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="H79" s="43" t="s">
+        <v>420</v>
+      </c>
+      <c r="I79" s="39"/>
+      <c r="J79" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K79" s="40"/>
+    </row>
+    <row r="80" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="49"/>
+      <c r="B80" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="C80" s="47">
+        <v>45735</v>
+      </c>
+      <c r="D80" s="42" t="s">
         <v>376</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="E80" s="48">
+        <v>9010001141627</v>
+      </c>
+      <c r="F80" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="G80" s="42" t="s">
+        <v>366</v>
+      </c>
+      <c r="H80" s="43" t="s">
+        <v>367</v>
+      </c>
+      <c r="I80" s="39"/>
+      <c r="J80" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K80" s="39"/>
+    </row>
+    <row r="81" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="49"/>
+      <c r="B81" s="35" t="s">
         <v>377</v>
       </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26" t="s">
+      <c r="C81" s="47">
+        <v>45887</v>
+      </c>
+      <c r="D81" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="E81" s="48">
+        <v>1010001205562</v>
+      </c>
+      <c r="F81" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="G81" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="H81" s="43" t="s">
+        <v>380</v>
+      </c>
+      <c r="I81" s="39"/>
+      <c r="J81" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="K7" s="57"/>
-    </row>
-    <row r="8" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="58" t="str">
-        <f>"関東財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"関東財務局*")&amp;"業者】"</f>
-        <v>関東財務局
-【計77業者】</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="11">
-        <v>40269</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E8" s="13">
-        <v>3010401058641</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14" t="s">
+      <c r="K81" s="40"/>
+    </row>
+    <row r="82" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="49"/>
+      <c r="B82" s="50" t="s">
+        <v>382</v>
+      </c>
+      <c r="C82" s="51">
+        <v>45908</v>
+      </c>
+      <c r="D82" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="E82" s="52">
+        <v>1010401137711</v>
+      </c>
+      <c r="F82" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="G82" s="54" t="s">
+        <v>421</v>
+      </c>
+      <c r="H82" s="53" t="s">
+        <v>384</v>
+      </c>
+      <c r="I82" s="55"/>
+      <c r="J82" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="K82" s="56"/>
+    </row>
+    <row r="83" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="49"/>
+      <c r="B83" s="50" t="s">
+        <v>396</v>
+      </c>
+      <c r="C83" s="51">
+        <v>46132</v>
+      </c>
+      <c r="D83" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="E83" s="52">
+        <v>9010001256136</v>
+      </c>
+      <c r="F83" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="54" t="s">
+        <v>397</v>
+      </c>
+      <c r="H83" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="I83" s="55"/>
+      <c r="J83" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="K83" s="56"/>
+    </row>
+    <row r="84" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="49"/>
+      <c r="B84" s="50" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="51">
+        <v>46178</v>
+      </c>
+      <c r="D84" s="42" t="s">
+        <v>409</v>
+      </c>
+      <c r="E84" s="52">
+        <v>9011101027550</v>
+      </c>
+      <c r="F84" s="53" t="s">
+        <v>410</v>
+      </c>
+      <c r="G84" s="54" t="s">
+        <v>407</v>
+      </c>
+      <c r="H84" s="53" t="s">
+        <v>411</v>
+      </c>
+      <c r="I84" s="55"/>
+      <c r="J84" s="55" t="s">
         <v>203</v>
       </c>
-      <c r="K8" s="59"/>
-    </row>
-    <row r="9" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="60"/>
-      <c r="B9" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="16">
-        <v>40340</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="E9" s="18">
-        <v>3010701023295</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="J9" s="19" t="s">
+      <c r="K84" s="56"/>
+    </row>
+    <row r="85" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="80"/>
+      <c r="B85" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="C85" s="81">
+        <v>46251</v>
+      </c>
+      <c r="D85" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="E85" s="82">
+        <v>6010001125005</v>
+      </c>
+      <c r="F85" s="83" t="s">
+        <v>425</v>
+      </c>
+      <c r="G85" s="57" t="s">
+        <v>426</v>
+      </c>
+      <c r="H85" s="83" t="s">
+        <v>427</v>
+      </c>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="K9" s="61"/>
-    </row>
-    <row r="10" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="62"/>
-      <c r="B10" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="16">
-        <v>40389</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="E10" s="18">
-        <v>5010401089313</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K10" s="61"/>
-    </row>
-    <row r="11" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="62"/>
-      <c r="B11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="16">
-        <v>40497</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="E11" s="18">
-        <v>5010501030903</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K11" s="61"/>
-    </row>
-    <row r="12" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="62"/>
-      <c r="B12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="16">
-        <v>40519</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" s="18">
-        <v>9010401089532</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K12" s="61"/>
-    </row>
-    <row r="13" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="62"/>
-      <c r="B13" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="16">
-        <v>40603</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="E13" s="18">
-        <v>6010401071583</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K13" s="61"/>
-    </row>
-    <row r="14" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="62"/>
-      <c r="B14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="16">
-        <v>40644</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="E14" s="18">
-        <v>9010001134572</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K14" s="61"/>
-    </row>
-    <row r="15" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="62"/>
-      <c r="B15" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="16">
-        <v>40681</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="E15" s="18">
-        <v>1010001067912</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K15" s="61"/>
-    </row>
-    <row r="16" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="62"/>
-      <c r="B16" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="16">
-        <v>40715</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="E16" s="18">
-        <v>8010001103611</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K16" s="61"/>
-    </row>
-    <row r="17" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="62"/>
-      <c r="B17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="16">
-        <v>40750</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="E17" s="18">
-        <v>5010601030547</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K17" s="61"/>
-    </row>
-    <row r="18" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="62"/>
-      <c r="B18" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="16">
-        <v>40798</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="E18" s="18">
-        <v>4010401058731</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K18" s="61"/>
-    </row>
-    <row r="19" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="62"/>
-      <c r="B19" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="16">
-        <v>40863</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="E19" s="18">
-        <v>7011101036066</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K19" s="61"/>
-    </row>
-    <row r="20" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="62"/>
-      <c r="B20" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="16">
-        <v>40954</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="E20" s="18">
-        <v>1011101057035</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K20" s="61"/>
-    </row>
-    <row r="21" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="62"/>
-      <c r="B21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="16">
-        <v>40966</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="E21" s="18">
-        <v>4010401084380</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K21" s="61"/>
-    </row>
-    <row r="22" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="62"/>
-      <c r="B22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="16">
-        <v>40996</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="E22" s="18">
-        <v>1010401095934</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>407</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K22" s="61"/>
-    </row>
-    <row r="23" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="62"/>
-      <c r="B23" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="16">
-        <v>41085</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="E23" s="18">
-        <v>6011101062006</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K23" s="61"/>
-    </row>
-    <row r="24" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="62"/>
-      <c r="B24" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="16">
-        <v>41122</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="E24" s="18">
-        <v>3700150006491</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K24" s="61"/>
-    </row>
-    <row r="25" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="62"/>
-      <c r="B25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="16">
-        <v>41264</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="E25" s="18">
-        <v>2010401087071</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K25" s="61"/>
-    </row>
-    <row r="26" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="62"/>
-      <c r="B26" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="22">
-        <v>41442</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="E26" s="18">
-        <v>6010401094452</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K26" s="61"/>
-    </row>
-    <row r="27" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="62"/>
-      <c r="B27" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="22">
-        <v>41451</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="E27" s="18">
-        <v>9010401099531</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K27" s="61"/>
-    </row>
-    <row r="28" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="62"/>
-      <c r="B28" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="22">
-        <v>41516</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="E28" s="18">
-        <v>6011101063994</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K28" s="61"/>
-    </row>
-    <row r="29" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="62"/>
-      <c r="B29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="22">
-        <v>41558</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" s="18">
-        <v>1020001100705</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K29" s="61"/>
-    </row>
-    <row r="30" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="62"/>
-      <c r="B30" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="22">
-        <v>41880</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="E30" s="18">
-        <v>9010401105000</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K30" s="61"/>
-    </row>
-    <row r="31" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="62"/>
-      <c r="B31" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="22">
-        <v>41969</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="E31" s="18">
-        <v>6011001005411</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K31" s="61"/>
-    </row>
-    <row r="32" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="62"/>
-      <c r="B32" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="22">
-        <v>42041</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="E32" s="18">
-        <v>6011001092945</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K32" s="61"/>
-    </row>
-    <row r="33" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="63"/>
-      <c r="B33" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="22">
-        <v>42234</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="E33" s="18">
-        <v>5010401114302</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K33" s="61"/>
-    </row>
-    <row r="34" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="63"/>
-      <c r="B34" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="22">
-        <v>42234</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="E34" s="18">
-        <v>4011001100453</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K34" s="61"/>
-    </row>
-    <row r="35" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="63"/>
-      <c r="B35" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="22">
-        <v>42340</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="E35" s="18">
-        <v>9010401113770</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H35" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K35" s="61"/>
-    </row>
-    <row r="36" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="63"/>
-      <c r="B36" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="22">
-        <v>42481</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="E36" s="18">
-        <v>1011001053935</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K36" s="61"/>
-    </row>
-    <row r="37" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="64"/>
-      <c r="B37" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="22">
-        <v>42506</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E37" s="18">
-        <v>8010001164001</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="H37" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K37" s="61"/>
-    </row>
-    <row r="38" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="63"/>
-      <c r="B38" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="23">
-        <v>42544</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="E38" s="18">
-        <v>4010001166406</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>403</v>
-      </c>
-      <c r="H38" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K38" s="61"/>
-    </row>
-    <row r="39" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="62"/>
-      <c r="B39" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="23">
-        <v>42704</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="E39" s="18">
-        <v>7700150006587</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="H39" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K39" s="61"/>
-    </row>
-    <row r="40" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="62"/>
-      <c r="B40" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="23">
-        <v>42830</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="E40" s="18">
-        <v>9011101071185</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="H40" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K40" s="61"/>
-    </row>
-    <row r="41" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="62"/>
-      <c r="B41" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="23">
-        <v>42919</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="E41" s="18">
-        <v>2010001057425</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="H41" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K41" s="61"/>
-    </row>
-    <row r="42" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="62"/>
-      <c r="B42" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="23">
-        <v>43013</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="E42" s="18">
-        <v>6011101080437</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="H42" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K42" s="61"/>
-    </row>
-    <row r="43" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="62"/>
-      <c r="B43" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="23">
-        <v>43060</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="E43" s="18">
-        <v>1011101032839</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="H43" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K43" s="61"/>
-    </row>
-    <row r="44" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="62"/>
-      <c r="B44" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="23">
-        <v>43067</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="E44" s="18">
-        <v>5010401069983</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>418</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>419</v>
-      </c>
-      <c r="H44" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K44" s="61"/>
-    </row>
-    <row r="45" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="62"/>
-      <c r="B45" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="23">
-        <v>43076</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E45" s="18">
-        <v>2010001183865</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="H45" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K45" s="61"/>
-    </row>
-    <row r="46" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="62"/>
-      <c r="B46" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="23">
-        <v>43117</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="E46" s="18">
-        <v>3011101071892</v>
-      </c>
-      <c r="F46" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" s="20" t="s">
-        <v>348</v>
-      </c>
-      <c r="H46" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K46" s="61"/>
-    </row>
-    <row r="47" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="62"/>
-      <c r="B47" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="23">
-        <v>43173</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="E47" s="18">
-        <v>8010601051334</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="H47" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K47" s="61"/>
-    </row>
-    <row r="48" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="62"/>
-      <c r="B48" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="23">
-        <v>43181</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="E48" s="18">
-        <v>1010401135178</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="H48" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K48" s="61"/>
-    </row>
-    <row r="49" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="62"/>
-      <c r="B49" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" s="23">
-        <v>43213</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E49" s="18">
-        <v>1010001188907</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H49" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K49" s="61"/>
-    </row>
-    <row r="50" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="62"/>
-      <c r="B50" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="23">
-        <v>43263</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="E50" s="18">
-        <v>3010001183897</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="H50" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K50" s="61"/>
-    </row>
-    <row r="51" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="62"/>
-      <c r="B51" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" s="23">
-        <v>43307</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="E51" s="18">
-        <v>8010001188396</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="G51" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="H51" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K51" s="61"/>
-    </row>
-    <row r="52" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="62"/>
-      <c r="B52" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" s="23">
-        <v>43308</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="E52" s="18">
-        <v>5011401019978</v>
-      </c>
-      <c r="F52" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="G52" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="H52" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K52" s="61"/>
-    </row>
-    <row r="53" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="62"/>
-      <c r="B53" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="23">
-        <v>43327</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="E53" s="18">
-        <v>4010701034738</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="G53" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H53" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K53" s="61"/>
-    </row>
-    <row r="54" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="62"/>
-      <c r="B54" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="23">
-        <v>43375</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="E54" s="24">
-        <v>4011001117670</v>
-      </c>
-      <c r="F54" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="G54" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="H54" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K54" s="61"/>
-    </row>
-    <row r="55" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="62"/>
-      <c r="B55" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="E55" s="24">
-        <v>3013301041741</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="H55" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K55" s="61"/>
-    </row>
-    <row r="56" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="62"/>
-      <c r="B56" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="E56" s="24">
-        <v>3010901038102</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="H56" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K56" s="61"/>
-    </row>
-    <row r="57" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="62"/>
-      <c r="B57" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="E57" s="24">
-        <v>5010001192707</v>
-      </c>
-      <c r="F57" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="G57" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H57" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K57" s="61"/>
-    </row>
-    <row r="58" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="62"/>
-      <c r="B58" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="E58" s="24">
-        <v>7013301041449</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>242</v>
-      </c>
-      <c r="G58" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="H58" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K58" s="61"/>
-    </row>
-    <row r="59" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="62"/>
-      <c r="B59" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="E59" s="24">
-        <v>3010001167611</v>
-      </c>
-      <c r="F59" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="G59" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="H59" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K59" s="61"/>
-    </row>
-    <row r="60" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="62"/>
-      <c r="B60" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="E60" s="24">
-        <v>3010401049814</v>
-      </c>
-      <c r="F60" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="G60" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="H60" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K60" s="61"/>
-    </row>
-    <row r="61" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="62"/>
-      <c r="B61" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="E61" s="24">
-        <v>2010001190192</v>
-      </c>
-      <c r="F61" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="H61" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="I61" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="J61" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K61" s="61"/>
-    </row>
-    <row r="62" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="62"/>
-      <c r="B62" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C62" s="23">
-        <v>43868</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="E62" s="24">
-        <v>5011801019594</v>
-      </c>
-      <c r="F62" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="H62" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K62" s="61"/>
-    </row>
-    <row r="63" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="62"/>
-      <c r="B63" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="23">
-        <v>43868</v>
-      </c>
-      <c r="D63" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="E63" s="24">
-        <v>3010001161300</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G63" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K63" s="61"/>
-    </row>
-    <row r="64" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="62"/>
-      <c r="B64" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C64" s="23">
-        <v>43887</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="E64" s="24">
-        <v>9011401020230</v>
-      </c>
-      <c r="F64" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="G64" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="H64" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K64" s="61"/>
-    </row>
-    <row r="65" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="62"/>
-      <c r="B65" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C65" s="23">
-        <v>43888</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="E65" s="24">
-        <v>9010401134148</v>
-      </c>
-      <c r="F65" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="G65" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="H65" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K65" s="61"/>
-    </row>
-    <row r="66" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="62"/>
-      <c r="B66" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C66" s="23">
-        <v>43899</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="E66" s="24">
-        <v>7040001086061</v>
-      </c>
-      <c r="F66" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="G66" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="H66" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K66" s="61"/>
-    </row>
-    <row r="67" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="62"/>
-      <c r="B67" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C67" s="23">
-        <v>43922</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="E67" s="24">
-        <v>6020001125152</v>
-      </c>
-      <c r="F67" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="G67" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="H67" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K67" s="61"/>
-    </row>
-    <row r="68" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="62"/>
-      <c r="B68" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C68" s="23">
-        <v>44056</v>
-      </c>
-      <c r="D68" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E68" s="24">
-        <v>7010001206332</v>
-      </c>
-      <c r="F68" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="G68" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="H68" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K68" s="61"/>
-    </row>
-    <row r="69" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="62"/>
-      <c r="B69" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C69" s="23">
-        <v>44070</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="E69" s="24">
-        <v>9011001103831</v>
-      </c>
-      <c r="F69" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="G69" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="I69" s="19"/>
-      <c r="J69" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K69" s="61"/>
-    </row>
-    <row r="70" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="62"/>
-      <c r="B70" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C70" s="23">
-        <v>44127</v>
-      </c>
-      <c r="D70" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="E70" s="24">
-        <v>8011001127534</v>
-      </c>
-      <c r="F70" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="G70" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="H70" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K70" s="61"/>
-    </row>
-    <row r="71" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="62"/>
-      <c r="B71" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="C71" s="23">
-        <v>44335</v>
-      </c>
-      <c r="D71" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="E71" s="24">
-        <v>6013201011825</v>
-      </c>
-      <c r="F71" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="G71" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="H71" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K71" s="61"/>
-    </row>
-    <row r="72" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="62"/>
-      <c r="B72" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="C72" s="23">
-        <v>44371</v>
-      </c>
-      <c r="D72" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="E72" s="24">
-        <v>8010401050511</v>
-      </c>
-      <c r="F72" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="G72" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="H72" s="21" t="s">
-        <v>406</v>
-      </c>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K72" s="61"/>
-    </row>
-    <row r="73" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="62"/>
-      <c r="B73" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C73" s="23">
-        <v>44403</v>
-      </c>
-      <c r="D73" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="E73" s="24">
-        <v>5010401134795</v>
-      </c>
-      <c r="F73" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="G73" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="H73" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K73" s="61"/>
-    </row>
-    <row r="74" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="62"/>
-      <c r="B74" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="C74" s="23">
-        <v>44650</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="E74" s="24">
-        <v>5012401017708</v>
-      </c>
-      <c r="F74" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="G74" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="H74" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K74" s="61"/>
-    </row>
-    <row r="75" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="62"/>
-      <c r="B75" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="C75" s="23">
-        <v>44650</v>
-      </c>
-      <c r="D75" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="E75" s="24">
-        <v>2040001094812</v>
-      </c>
-      <c r="F75" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="G75" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="H75" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="I75" s="19"/>
-      <c r="J75" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K75" s="61"/>
-    </row>
-    <row r="76" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="62"/>
-      <c r="B76" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="C76" s="23">
-        <v>44650</v>
-      </c>
-      <c r="D76" s="20" t="s">
-        <v>313</v>
-      </c>
-      <c r="E76" s="24">
-        <v>8013301009057</v>
-      </c>
-      <c r="F76" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="G76" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="H76" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K76" s="61"/>
-    </row>
-    <row r="77" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="62"/>
-      <c r="B77" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="C77" s="23">
-        <v>44978</v>
-      </c>
-      <c r="D77" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="E77" s="24">
-        <v>4010401049813</v>
-      </c>
-      <c r="F77" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G77" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="H77" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K77" s="61"/>
-    </row>
-    <row r="78" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="65"/>
-      <c r="B78" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="C78" s="23">
-        <v>45254</v>
-      </c>
-      <c r="D78" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="E78" s="24">
-        <v>3010401113537</v>
-      </c>
-      <c r="F78" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="G78" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="H78" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K78" s="61"/>
-    </row>
-    <row r="79" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="65"/>
-      <c r="B79" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="C79" s="23">
-        <v>45275</v>
-      </c>
-      <c r="D79" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="E79" s="24">
-        <v>6011101086450</v>
-      </c>
-      <c r="F79" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="G79" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="H79" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K79" s="61"/>
-    </row>
-    <row r="80" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="65"/>
-      <c r="B80" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="C80" s="23">
-        <v>45735</v>
-      </c>
-      <c r="D80" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="E80" s="24">
-        <v>9010001141627</v>
-      </c>
-      <c r="F80" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="G80" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="H80" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="K80" s="19"/>
-    </row>
-    <row r="81" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="65"/>
-      <c r="B81" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="C81" s="75">
-        <v>45887</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>382</v>
-      </c>
-      <c r="E81" s="76">
-        <v>1010001205562</v>
-      </c>
-      <c r="F81" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="G81" s="78" t="s">
-        <v>381</v>
-      </c>
-      <c r="H81" s="77" t="s">
-        <v>383</v>
-      </c>
-      <c r="I81" s="79"/>
-      <c r="J81" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="K81" s="80"/>
-    </row>
-    <row r="82" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="65"/>
-      <c r="B82" s="74" t="s">
-        <v>385</v>
-      </c>
-      <c r="C82" s="75">
-        <v>45908</v>
-      </c>
-      <c r="D82" s="20" t="s">
-        <v>386</v>
-      </c>
-      <c r="E82" s="76">
-        <v>1010401137711</v>
-      </c>
-      <c r="F82" s="77" t="s">
-        <v>142</v>
-      </c>
-      <c r="G82" s="78" t="s">
-        <v>424</v>
-      </c>
-      <c r="H82" s="77" t="s">
-        <v>387</v>
-      </c>
-      <c r="I82" s="79"/>
-      <c r="J82" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="K82" s="80"/>
-    </row>
-    <row r="83" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="65"/>
-      <c r="B83" s="74" t="s">
-        <v>399</v>
-      </c>
-      <c r="C83" s="75">
-        <v>46132</v>
-      </c>
-      <c r="D83" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="E83" s="76">
-        <v>9010001256136</v>
-      </c>
-      <c r="F83" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="G83" s="78" t="s">
-        <v>400</v>
-      </c>
-      <c r="H83" s="77" t="s">
-        <v>401</v>
-      </c>
-      <c r="I83" s="79"/>
-      <c r="J83" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="K83" s="80"/>
-    </row>
-    <row r="84" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
-      <c r="B84" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="C84" s="81">
-        <v>46178</v>
-      </c>
-      <c r="D84" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="E84" s="82">
-        <v>9011101027550</v>
-      </c>
-      <c r="F84" s="83" t="s">
-        <v>413</v>
-      </c>
-      <c r="G84" s="25" t="s">
-        <v>410</v>
-      </c>
-      <c r="H84" s="83" t="s">
-        <v>414</v>
-      </c>
-      <c r="I84" s="26"/>
-      <c r="J84" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="K84" s="57"/>
-    </row>
-    <row r="85" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="60" t="str">
-        <f>"東海財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"東海財務局*")&amp;"業者】"</f>
+      <c r="K85" s="26"/>
+    </row>
+    <row r="86" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="34" t="str">
+        <f>"東海財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"東海財務局*")&amp;"業者】"</f>
         <v>東海財務局
 【計1業者】</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B86" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="C85" s="28">
+      <c r="C86" s="59">
         <v>40575</v>
       </c>
-      <c r="D85" s="29" t="s">
-        <v>315</v>
-      </c>
-      <c r="E85" s="30">
+      <c r="D86" s="60" t="s">
+        <v>314</v>
+      </c>
+      <c r="E86" s="61">
         <v>5200001003514</v>
       </c>
-      <c r="F85" s="27" t="s">
+      <c r="F86" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="G85" s="29" t="s">
+      <c r="G86" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="H85" s="27" t="s">
+      <c r="H86" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="I85" s="31"/>
-      <c r="J85" s="31" t="s">
+      <c r="I86" s="62"/>
+      <c r="J86" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="K85" s="67"/>
-    </row>
-    <row r="86" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="58" t="str">
-        <f>"北陸財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"北陸財務局*")&amp;"業者】"</f>
+      <c r="K86" s="63"/>
+    </row>
+    <row r="87" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="27" t="str">
+        <f>"北陸財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"北陸財務局*")&amp;"業者】"</f>
         <v>北陸財務局
 【計1業者】</v>
       </c>
-      <c r="B86" s="32" t="s">
+      <c r="B87" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C86" s="33">
+      <c r="C87" s="65">
         <v>41075</v>
       </c>
-      <c r="D86" s="34" t="s">
+      <c r="D87" s="66" t="s">
+        <v>315</v>
+      </c>
+      <c r="E87" s="67">
+        <v>3210001014413</v>
+      </c>
+      <c r="F87" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="G87" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="H87" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="I87" s="62"/>
+      <c r="J87" s="62" t="s">
+        <v>198</v>
+      </c>
+      <c r="K87" s="68"/>
+    </row>
+    <row r="88" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="69" t="s">
+        <v>352</v>
+      </c>
+      <c r="B88" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="29">
+        <v>42174</v>
+      </c>
+      <c r="D88" s="70" t="s">
         <v>316</v>
       </c>
-      <c r="E86" s="35">
-        <v>3210001014413</v>
-      </c>
-      <c r="F86" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="G86" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="H86" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="I86" s="31"/>
-      <c r="J86" s="31" t="s">
+      <c r="E88" s="31">
+        <v>2120001137521</v>
+      </c>
+      <c r="F88" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="G88" s="70" t="s">
+        <v>98</v>
+      </c>
+      <c r="H88" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="I88" s="32"/>
+      <c r="J88" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="K86" s="68"/>
-    </row>
-    <row r="87" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="69" t="s">
+      <c r="K88" s="72"/>
+    </row>
+    <row r="89" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="34"/>
+      <c r="B89" s="35" t="s">
+        <v>353</v>
+      </c>
+      <c r="C89" s="36">
+        <v>45673</v>
+      </c>
+      <c r="D89" s="42" t="s">
+        <v>354</v>
+      </c>
+      <c r="E89" s="38">
+        <v>1120001059675</v>
+      </c>
+      <c r="F89" s="73" t="s">
         <v>355</v>
       </c>
-      <c r="B87" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C87" s="11">
-        <v>42174</v>
-      </c>
-      <c r="D87" s="36" t="s">
-        <v>317</v>
-      </c>
-      <c r="E87" s="13">
-        <v>2120001137521</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="G87" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="I87" s="14"/>
-      <c r="J87" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="K87" s="70"/>
-    </row>
-    <row r="88" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="60"/>
-      <c r="B88" s="15" t="s">
+      <c r="G89" s="42" t="s">
         <v>356</v>
       </c>
-      <c r="C88" s="16">
-        <v>45673</v>
-      </c>
-      <c r="D88" s="20" t="s">
+      <c r="H89" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="E88" s="18">
-        <v>1120001059675</v>
-      </c>
-      <c r="F88" s="38" t="s">
+      <c r="I89" s="39"/>
+      <c r="J89" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="K89" s="74"/>
+    </row>
+    <row r="90" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="20"/>
+      <c r="B90" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="G88" s="20" t="s">
+      <c r="C90" s="22">
+        <v>45688</v>
+      </c>
+      <c r="D90" s="57" t="s">
         <v>359</v>
       </c>
-      <c r="H88" s="15" t="s">
+      <c r="E90" s="24">
+        <v>9120001075640</v>
+      </c>
+      <c r="F90" s="75" t="s">
         <v>360</v>
       </c>
-      <c r="I88" s="19"/>
-      <c r="J88" s="19" t="s">
+      <c r="G90" s="57" t="s">
+        <v>361</v>
+      </c>
+      <c r="H90" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="I90" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="K88" s="71"/>
-    </row>
-    <row r="89" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="56"/>
-      <c r="B89" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="C89" s="50">
-        <v>45688</v>
-      </c>
-      <c r="D89" s="25" t="s">
-        <v>362</v>
-      </c>
-      <c r="E89" s="52">
-        <v>9120001075640</v>
-      </c>
-      <c r="F89" s="72" t="s">
-        <v>363</v>
-      </c>
-      <c r="G89" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="H89" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="I89" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="J89" s="26"/>
-      <c r="K89" s="73"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="40" t="s">
+      <c r="J90" s="25"/>
+      <c r="K90" s="76"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="77" t="s">
         <v>219</v>
       </c>
-      <c r="B90" s="40"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="41"/>
-      <c r="E90" s="41"/>
-      <c r="F90" s="40"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="40"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="40"/>
-      <c r="B91" s="40"/>
-      <c r="C91" s="40"/>
-      <c r="D91" s="41"/>
-      <c r="E91" s="41"/>
-      <c r="F91" s="40"/>
-      <c r="G91" s="41"/>
-      <c r="H91" s="40"/>
+      <c r="B91" s="77"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="78"/>
+      <c r="E91" s="78"/>
+      <c r="F91" s="77"/>
+      <c r="G91" s="78"/>
+      <c r="H91" s="77"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="40"/>
-      <c r="B92" s="40"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="41"/>
-      <c r="F92" s="40"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="40"/>
+      <c r="A92" s="77"/>
+      <c r="B92" s="77"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="78"/>
+      <c r="E92" s="78"/>
+      <c r="F92" s="77"/>
+      <c r="G92" s="78"/>
+      <c r="H92" s="77"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="40"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="40"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="40"/>
-      <c r="G93" s="41"/>
-      <c r="H93" s="40"/>
+      <c r="A93" s="77"/>
+      <c r="B93" s="77"/>
+      <c r="C93" s="77"/>
+      <c r="D93" s="78"/>
+      <c r="E93" s="78"/>
+      <c r="F93" s="77"/>
+      <c r="G93" s="78"/>
+      <c r="H93" s="77"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94" s="77"/>
+      <c r="B94" s="77"/>
+      <c r="C94" s="77"/>
+      <c r="D94" s="78"/>
+      <c r="E94" s="78"/>
+      <c r="F94" s="77"/>
+      <c r="G94" s="78"/>
+      <c r="H94" s="77"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:K5" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -7932,249 +7971,17 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
-    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A85:A86" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A86:A87" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="69" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <rowBreaks count="3" manualBreakCount="3">
+  <rowBreaks count="4" manualBreakCount="4">
     <brk id="35" max="10" man="1"/>
     <brk id="50" max="10" man="1"/>
     <brk id="65" max="10" man="1"/>
+    <brk id="81" max="10" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100983B318F74802D4ABEFADEC269058BE9" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="1908bdf7e2a759c5d3bec18ce44fe038">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32c3a57c-5296-4003-b936-9ab25ad0923d" xmlns:ns3="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3877253f6ba9ebfbd06dda58d5ecc6dc" ns2:_="" ns3:_="">
-    <xsd:import namespace="32c3a57c-5296-4003-b936-9ab25ad0923d"/>
-    <xsd:import namespace="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="32c3a57c-5296-4003-b936-9ab25ad0923d" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1e1c6816-2a4f-4461-93c7-8dd281d6228d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c52ab56e-ac1a-462d-a023-20ac0a678e2a}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="32c3a57c-5296-4003-b936-9ab25ad0923d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22F7B942-00C4-4CCA-9D47-F052EC154F5A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7286210E-9387-43B0-B5AC-B2D6CC698180}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D37A222A-D56C-4197-A9D8-4E4C7A2E4328}"/>
 </file>
--- a/data/previous.xlsx
+++ b/data/previous.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7DD92-A4EA-4BAD-BF0F-6288B1C0BB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="13_ncr:1_{84C4A5A4-774F-413D-BA65-C4BA17ABD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEDF5184-7EE2-4949-B3BA-2F6507098D87}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資金移動" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">資金移動!$A$4:$K$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">資金移動!$A$1:$K$91</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">資金移動!$A$1:$K$90</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">資金移動!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="425">
   <si>
     <t>登録番号</t>
     <rPh sb="0" eb="2">
@@ -285,30 +285,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>関東財務局長
-第00012号</t>
-    <rPh sb="0" eb="2">
-      <t>カントウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ザイム</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キョクチョウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ゴウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>100-6150</t>
-  </si>
-  <si>
-    <t>03-5156-1111</t>
   </si>
   <si>
     <t>関東財務局長
@@ -967,20 +944,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>東京都千代田区永田町２－１１－１
-山王パークタワー</t>
-    <rPh sb="3" eb="7">
-      <t>チヨダク</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ナガタチョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>サンノウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>東京都港区虎ノ門５－１－５
 メトロシティ神谷町７階</t>
     <rPh sb="0" eb="2">
@@ -2688,9 +2651,6 @@
     <t>Ｓｐｅｅｄ　Ｍｏｎｅｙ　Ｔｒａｎｓｆｅｒ　Ｊａｐａｎ株式会社</t>
   </si>
   <si>
-    <t>株式会社ＮＴＴドコモ</t>
-  </si>
-  <si>
     <t>ＮＴＴスマートトレード株式会社</t>
   </si>
   <si>
@@ -3024,29 +2984,6 @@
   </si>
   <si>
     <t>103-0027</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>東京都中央区日本橋３－２－２
-オオタケ第７ビル３階</t>
-    <rPh sb="0" eb="3">
-      <t>トウキョウト</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>チュウオウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>ニホンバシ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>カイ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3653,6 +3590,23 @@
   </si>
   <si>
     <t>03-6694-4276</t>
+  </si>
+  <si>
+    <t>東京都中央区日本橋３－２－２
+シーザー八重洲ビル３階</t>
+    <rPh sb="0" eb="3">
+      <t>トウキョウト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チュウオウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニホンバシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4825,6 +4779,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4893,18 +4859,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="24" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5302,16 +5256,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.7265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43" style="79" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="79" customWidth="1"/>
+    <col min="4" max="4" width="43" style="83" customWidth="1"/>
+    <col min="5" max="5" width="15.7265625" style="83" customWidth="1"/>
     <col min="6" max="6" width="12.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.90625" style="79" customWidth="1"/>
+    <col min="7" max="7" width="39.90625" style="83" customWidth="1"/>
     <col min="8" max="8" width="16.7265625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
@@ -5333,7 +5287,7 @@
     </row>
     <row r="2" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="89" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B2" s="89"/>
       <c r="C2" s="89"/>
@@ -5345,8 +5299,8 @@
     </row>
     <row r="3" spans="1:11" s="9" customFormat="1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="str">
-        <f>"【全業者数："&amp;COUNTA($B$5:$B$861)&amp;"】"</f>
-        <v>【全業者数：85】</v>
+        <f>"【全業者数："&amp;COUNTA($B$5:$B$860)&amp;"】"</f>
+        <v>【全業者数：84】</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="7"/>
@@ -5356,7 +5310,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
       <c r="I3" s="93">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="J3" s="93"/>
       <c r="K3" s="93"/>
@@ -5375,7 +5329,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="94" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>4</v>
@@ -5387,7 +5341,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="90" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J4" s="91"/>
       <c r="K4" s="92"/>
@@ -5402,82 +5356,82 @@
       <c r="G5" s="95"/>
       <c r="H5" s="85"/>
       <c r="I5" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="str">
-        <f>"北海道財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"北海道財務局*")&amp;"業者】"</f>
+        <f>"北海道財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"北海道財務局*")&amp;"業者】"</f>
         <v>北海道財務局
 【計2業者】</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C6" s="14">
         <v>44592</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E6" s="16">
         <v>5010001125807</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I6" s="18"/>
       <c r="J6" s="18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
       <c r="B7" s="21" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C7" s="22">
         <v>45833</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E7" s="24">
         <v>9010401124520</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="25" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K7" s="26"/>
     </row>
     <row r="8" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="str">
-        <f>"関東財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"関東財務局*")&amp;"業者】"</f>
+        <f>"関東財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"関東財務局*")&amp;"業者】"</f>
         <v>関東財務局
-【計78業者】</v>
+【計77業者】</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>8</v>
@@ -5486,23 +5440,23 @@
         <v>40269</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E8" s="31">
         <v>3010401058641</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H8" s="28" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="32"/>
       <c r="J8" s="32" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K8" s="33"/>
     </row>
@@ -5515,25 +5469,25 @@
         <v>40340</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E9" s="38">
         <v>3010701023295</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="I9" s="39" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J9" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K9" s="40"/>
     </row>
@@ -5546,23 +5500,23 @@
         <v>40389</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E10" s="38">
         <v>5010401089313</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H10" s="35" t="s">
         <v>12</v>
       </c>
       <c r="I10" s="39"/>
       <c r="J10" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K10" s="40"/>
     </row>
@@ -5575,7 +5529,7 @@
         <v>40497</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E11" s="38">
         <v>5010501030903</v>
@@ -5584,14 +5538,14 @@
         <v>15</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I11" s="39"/>
       <c r="J11" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K11" s="40"/>
     </row>
@@ -5604,25 +5558,25 @@
         <v>40519</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E12" s="38">
         <v>9010401089532</v>
       </c>
       <c r="F12" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G12" s="42" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H12" s="43" t="s">
         <v>16</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K12" s="40"/>
     </row>
@@ -5635,25 +5589,25 @@
         <v>40603</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E13" s="38">
         <v>6010401071583</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G13" s="42" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H13" s="43" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K13" s="40"/>
     </row>
@@ -5666,52 +5620,54 @@
         <v>40644</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E14" s="38">
         <v>9010001134572</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G14" s="42" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I14" s="39"/>
       <c r="J14" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K14" s="40"/>
     </row>
-    <row r="15" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="41"/>
       <c r="B15" s="35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="36">
-        <v>40681</v>
+        <v>40715</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E15" s="38">
-        <v>1010001067912</v>
+        <v>8010001103611</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="G15" s="42" t="s">
-        <v>62</v>
+        <v>383</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="39"/>
+        <v>133</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>195</v>
+      </c>
       <c r="J15" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K15" s="40"/>
     </row>
@@ -5721,86 +5677,86 @@
         <v>22</v>
       </c>
       <c r="C16" s="36">
-        <v>40715</v>
+        <v>40750</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E16" s="38">
-        <v>8010001103611</v>
+        <v>5010601030547</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="G16" s="42" t="s">
-        <v>388</v>
+        <v>23</v>
       </c>
       <c r="H16" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>198</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="I16" s="39"/>
       <c r="J16" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K16" s="40"/>
     </row>
     <row r="17" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="41"/>
       <c r="B17" s="35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="36">
-        <v>40750</v>
+        <v>40798</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E17" s="38">
-        <v>5010601030547</v>
+        <v>4010401058731</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="G17" s="42" t="s">
-        <v>25</v>
+        <v>231</v>
       </c>
       <c r="H17" s="43" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="I17" s="39"/>
       <c r="J17" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K17" s="40"/>
     </row>
     <row r="18" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="41"/>
       <c r="B18" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="36">
+        <v>40863</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" s="38">
+        <v>7011101036066</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>407</v>
+      </c>
+      <c r="H18" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="36">
-        <v>40798</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="E18" s="38">
-        <v>4010401058731</v>
-      </c>
-      <c r="F18" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="G18" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="H18" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="I18" s="39"/>
+      <c r="I18" s="39" t="s">
+        <v>195</v>
+      </c>
       <c r="J18" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K18" s="40"/>
     </row>
@@ -5810,28 +5766,26 @@
         <v>28</v>
       </c>
       <c r="C19" s="36">
-        <v>40863</v>
+        <v>40954</v>
       </c>
       <c r="D19" s="42" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E19" s="38">
-        <v>7011101036066</v>
+        <v>1011101057035</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="G19" s="42" t="s">
-        <v>412</v>
+        <v>29</v>
       </c>
       <c r="H19" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>198</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="I19" s="39"/>
       <c r="J19" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K19" s="40"/>
     </row>
@@ -5841,55 +5795,55 @@
         <v>30</v>
       </c>
       <c r="C20" s="36">
-        <v>40954</v>
+        <v>40966</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E20" s="38">
-        <v>1011101057035</v>
+        <v>4010401084380</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="G20" s="42" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H20" s="43" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I20" s="39"/>
       <c r="J20" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K20" s="40"/>
     </row>
     <row r="21" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41"/>
       <c r="B21" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="36">
+        <v>40996</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="38">
+        <v>1010401095934</v>
+      </c>
+      <c r="F21" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="36">
-        <v>40966</v>
-      </c>
-      <c r="D21" s="42" t="s">
-        <v>267</v>
-      </c>
-      <c r="E21" s="38">
-        <v>4010401084380</v>
-      </c>
-      <c r="F21" s="43" t="s">
-        <v>36</v>
-      </c>
       <c r="G21" s="42" t="s">
-        <v>49</v>
+        <v>399</v>
       </c>
       <c r="H21" s="43" t="s">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="I21" s="39"/>
       <c r="J21" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K21" s="40"/>
     </row>
@@ -5899,26 +5853,26 @@
         <v>33</v>
       </c>
       <c r="C22" s="36">
-        <v>40996</v>
+        <v>41085</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E22" s="38">
-        <v>1010401095934</v>
+        <v>6011101062006</v>
       </c>
       <c r="F22" s="43" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>404</v>
+        <v>96</v>
       </c>
       <c r="H22" s="43" t="s">
-        <v>405</v>
+        <v>138</v>
       </c>
       <c r="I22" s="39"/>
       <c r="J22" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K22" s="40"/>
     </row>
@@ -5928,55 +5882,55 @@
         <v>35</v>
       </c>
       <c r="C23" s="36">
-        <v>41085</v>
+        <v>41122</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E23" s="38">
-        <v>6011101062006</v>
+        <v>3700150006491</v>
       </c>
       <c r="F23" s="43" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="G23" s="42" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="H23" s="43" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="I23" s="39"/>
       <c r="J23" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K23" s="40"/>
     </row>
     <row r="24" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="41"/>
       <c r="B24" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="36">
-        <v>41122</v>
+        <v>41264</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E24" s="38">
-        <v>3700150006491</v>
+        <v>2010401087071</v>
       </c>
       <c r="F24" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="H24" s="43" t="s">
         <v>142</v>
-      </c>
-      <c r="G24" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" s="43" t="s">
-        <v>250</v>
       </c>
       <c r="I24" s="39"/>
       <c r="J24" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K24" s="40"/>
     </row>
@@ -5985,259 +5939,261 @@
       <c r="B25" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="36">
-        <v>41264</v>
+      <c r="C25" s="44">
+        <v>41442</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E25" s="38">
-        <v>2010401087071</v>
+        <v>6010401094452</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="G25" s="42" t="s">
-        <v>218</v>
+        <v>417</v>
       </c>
       <c r="H25" s="43" t="s">
-        <v>145</v>
+        <v>408</v>
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K25" s="40"/>
     </row>
     <row r="26" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="41"/>
       <c r="B26" s="35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" s="44">
-        <v>41442</v>
+        <v>41451</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E26" s="38">
-        <v>6010401094452</v>
+        <v>9010401099531</v>
       </c>
       <c r="F26" s="43" t="s">
-        <v>129</v>
+        <v>314</v>
       </c>
       <c r="G26" s="42" t="s">
-        <v>422</v>
+        <v>315</v>
       </c>
       <c r="H26" s="43" t="s">
-        <v>413</v>
+        <v>144</v>
       </c>
       <c r="I26" s="39"/>
       <c r="J26" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K26" s="40"/>
     </row>
     <row r="27" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41"/>
       <c r="B27" s="35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="44">
-        <v>41451</v>
+        <v>41516</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E27" s="38">
-        <v>9010401099531</v>
+        <v>6011101063994</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>318</v>
+        <v>34</v>
       </c>
       <c r="G27" s="42" t="s">
-        <v>319</v>
+        <v>123</v>
       </c>
       <c r="H27" s="43" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I27" s="39"/>
       <c r="J27" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K27" s="40"/>
     </row>
     <row r="28" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="41"/>
       <c r="B28" s="35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="44">
-        <v>41516</v>
+        <v>41558</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>274</v>
+        <v>146</v>
       </c>
       <c r="E28" s="38">
-        <v>6011101063994</v>
+        <v>1020001100705</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="G28" s="42" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="H28" s="43" t="s">
         <v>148</v>
       </c>
       <c r="I28" s="39"/>
       <c r="J28" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K28" s="40"/>
     </row>
     <row r="29" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="41"/>
       <c r="B29" s="35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="44">
-        <v>41558</v>
+        <v>41880</v>
       </c>
       <c r="D29" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="E29" s="38">
+        <v>9010401105000</v>
+      </c>
+      <c r="F29" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="38">
-        <v>1020001100705</v>
-      </c>
-      <c r="F29" s="43" t="s">
+      <c r="G29" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" s="43" t="s">
         <v>150</v>
-      </c>
-      <c r="G29" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" s="43" t="s">
-        <v>151</v>
       </c>
       <c r="I29" s="39"/>
       <c r="J29" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K29" s="40"/>
     </row>
     <row r="30" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
       <c r="B30" s="35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="44">
-        <v>41880</v>
+        <v>41969</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>333</v>
+        <v>271</v>
       </c>
       <c r="E30" s="38">
-        <v>9010401105000</v>
+        <v>6011001005411</v>
       </c>
       <c r="F30" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="43" t="s">
         <v>152</v>
-      </c>
-      <c r="G30" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="H30" s="43" t="s">
-        <v>153</v>
       </c>
       <c r="I30" s="39"/>
       <c r="J30" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K30" s="40"/>
     </row>
     <row r="31" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="41"/>
       <c r="B31" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" s="44">
-        <v>41969</v>
+        <v>42041</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E31" s="38">
-        <v>6011001005411</v>
+        <v>6011001092945</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="G31" s="42" t="s">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="H31" s="43" t="s">
-        <v>155</v>
+        <v>330</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K31" s="40"/>
     </row>
     <row r="32" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="41"/>
+      <c r="A32" s="45"/>
       <c r="B32" s="35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="44">
-        <v>42041</v>
+        <v>42234</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E32" s="38">
-        <v>6011001092945</v>
+        <v>5010401114302</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="G32" s="42" t="s">
-        <v>336</v>
+        <v>60</v>
       </c>
       <c r="H32" s="43" t="s">
-        <v>334</v>
+        <v>153</v>
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K32" s="40"/>
     </row>
     <row r="33" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45"/>
       <c r="B33" s="35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="44">
         <v>42234</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E33" s="38">
-        <v>5010401114302</v>
+        <v>4011001100453</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>143</v>
+        <v>314</v>
       </c>
       <c r="G33" s="42" t="s">
-        <v>63</v>
+        <v>324</v>
       </c>
       <c r="H33" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="I33" s="39"/>
+        <v>155</v>
+      </c>
+      <c r="I33" s="39" t="s">
+        <v>200</v>
+      </c>
       <c r="J33" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K33" s="40"/>
     </row>
@@ -6247,28 +6203,26 @@
         <v>48</v>
       </c>
       <c r="C34" s="44">
-        <v>42234</v>
+        <v>42340</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E34" s="38">
-        <v>4011001100453</v>
+        <v>9010401113770</v>
       </c>
       <c r="F34" s="43" t="s">
-        <v>318</v>
+        <v>143</v>
       </c>
       <c r="G34" s="42" t="s">
-        <v>328</v>
+        <v>49</v>
       </c>
       <c r="H34" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="I34" s="39" t="s">
-        <v>203</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="I34" s="39"/>
       <c r="J34" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K34" s="40"/>
     </row>
@@ -6278,393 +6232,393 @@
         <v>50</v>
       </c>
       <c r="C35" s="44">
-        <v>42340</v>
+        <v>42481</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E35" s="38">
-        <v>9010401113770</v>
+        <v>1011001053935</v>
       </c>
       <c r="F35" s="43" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G35" s="42" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="H35" s="43" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I35" s="39"/>
       <c r="J35" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K35" s="40"/>
     </row>
     <row r="36" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="45"/>
+      <c r="A36" s="46"/>
       <c r="B36" s="35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" s="44">
-        <v>42481</v>
+        <v>42506</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E36" s="38">
-        <v>1011001053935</v>
+        <v>8010001164001</v>
       </c>
       <c r="F36" s="43" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G36" s="42" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H36" s="43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I36" s="39"/>
       <c r="J36" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K36" s="40"/>
     </row>
     <row r="37" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="46"/>
+      <c r="A37" s="45"/>
       <c r="B37" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="44">
-        <v>42506</v>
+        <v>52</v>
+      </c>
+      <c r="C37" s="47">
+        <v>42544</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>281</v>
+        <v>364</v>
       </c>
       <c r="E37" s="38">
-        <v>8010001164001</v>
+        <v>4010001166406</v>
       </c>
       <c r="F37" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="G37" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="H37" s="43" t="s">
         <v>161</v>
-      </c>
-      <c r="G37" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="H37" s="43" t="s">
-        <v>162</v>
       </c>
       <c r="I37" s="39"/>
       <c r="J37" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K37" s="40"/>
     </row>
     <row r="38" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="45"/>
+      <c r="A38" s="41"/>
       <c r="B38" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="47">
-        <v>42544</v>
+        <v>42704</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>369</v>
+        <v>278</v>
       </c>
       <c r="E38" s="38">
-        <v>4010001166406</v>
+        <v>7700150006587</v>
       </c>
       <c r="F38" s="43" t="s">
-        <v>399</v>
+        <v>320</v>
       </c>
       <c r="G38" s="42" t="s">
-        <v>400</v>
+        <v>321</v>
       </c>
       <c r="H38" s="43" t="s">
-        <v>164</v>
+        <v>325</v>
       </c>
       <c r="I38" s="39"/>
       <c r="J38" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K38" s="40"/>
     </row>
     <row r="39" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="41"/>
       <c r="B39" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C39" s="47">
-        <v>42704</v>
+        <v>42830</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E39" s="38">
-        <v>7700150006587</v>
+        <v>9011101071185</v>
       </c>
       <c r="F39" s="43" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="G39" s="42" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="H39" s="43" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="I39" s="39"/>
       <c r="J39" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K39" s="40"/>
     </row>
     <row r="40" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="41"/>
       <c r="B40" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="47">
+        <v>42919</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" s="38">
+        <v>2010001057425</v>
+      </c>
+      <c r="F40" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="G40" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="47">
-        <v>42830</v>
-      </c>
-      <c r="D40" s="42" t="s">
-        <v>283</v>
-      </c>
-      <c r="E40" s="38">
-        <v>9011101071185</v>
-      </c>
-      <c r="F40" s="43" t="s">
-        <v>346</v>
-      </c>
-      <c r="G40" s="42" t="s">
-        <v>350</v>
-      </c>
       <c r="H40" s="43" t="s">
-        <v>351</v>
+        <v>163</v>
       </c>
       <c r="I40" s="39"/>
       <c r="J40" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K40" s="40"/>
     </row>
     <row r="41" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="41"/>
       <c r="B41" s="35" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C41" s="47">
-        <v>42919</v>
+        <v>43013</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E41" s="38">
-        <v>2010001057425</v>
+        <v>6011101080437</v>
       </c>
       <c r="F41" s="43" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G41" s="42" t="s">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="H41" s="43" t="s">
-        <v>166</v>
+        <v>333</v>
       </c>
       <c r="I41" s="39"/>
       <c r="J41" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K41" s="40"/>
     </row>
     <row r="42" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="41"/>
       <c r="B42" s="35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C42" s="47">
-        <v>43013</v>
+        <v>43060</v>
       </c>
       <c r="D42" s="42" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E42" s="38">
-        <v>6011101080437</v>
+        <v>1011101032839</v>
       </c>
       <c r="F42" s="43" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="G42" s="42" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="H42" s="43" t="s">
-        <v>337</v>
+        <v>166</v>
       </c>
       <c r="I42" s="39"/>
       <c r="J42" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K42" s="40"/>
     </row>
     <row r="43" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="41"/>
       <c r="B43" s="35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C43" s="47">
-        <v>43060</v>
+        <v>43067</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>286</v>
+        <v>409</v>
       </c>
       <c r="E43" s="38">
-        <v>1011101032839</v>
+        <v>5010401069983</v>
       </c>
       <c r="F43" s="43" t="s">
-        <v>167</v>
+        <v>410</v>
       </c>
       <c r="G43" s="42" t="s">
-        <v>168</v>
+        <v>411</v>
       </c>
       <c r="H43" s="43" t="s">
-        <v>169</v>
+        <v>412</v>
       </c>
       <c r="I43" s="39"/>
       <c r="J43" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K43" s="40"/>
     </row>
     <row r="44" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
       <c r="B44" s="35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C44" s="47">
-        <v>43067</v>
+        <v>43076</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>414</v>
+        <v>283</v>
       </c>
       <c r="E44" s="38">
-        <v>5010401069983</v>
+        <v>2010001183865</v>
       </c>
       <c r="F44" s="43" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="G44" s="42" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="H44" s="43" t="s">
-        <v>417</v>
+        <v>168</v>
       </c>
       <c r="I44" s="39"/>
       <c r="J44" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K44" s="40"/>
     </row>
     <row r="45" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="41"/>
       <c r="B45" s="35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" s="47">
-        <v>43076</v>
+        <v>43117</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E45" s="38">
-        <v>2010001183865</v>
+        <v>3011101071892</v>
       </c>
       <c r="F45" s="43" t="s">
-        <v>402</v>
+        <v>34</v>
       </c>
       <c r="G45" s="42" t="s">
-        <v>401</v>
+        <v>340</v>
       </c>
       <c r="H45" s="43" t="s">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="I45" s="39"/>
       <c r="J45" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K45" s="40"/>
     </row>
     <row r="46" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="41"/>
       <c r="B46" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C46" s="47">
-        <v>43117</v>
+        <v>43173</v>
       </c>
       <c r="D46" s="42" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E46" s="38">
-        <v>3011101071892</v>
+        <v>8010601051334</v>
       </c>
       <c r="F46" s="43" t="s">
-        <v>36</v>
+        <v>334</v>
       </c>
       <c r="G46" s="42" t="s">
-        <v>345</v>
+        <v>424</v>
       </c>
       <c r="H46" s="43" t="s">
-        <v>255</v>
+        <v>169</v>
       </c>
       <c r="I46" s="39"/>
       <c r="J46" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K46" s="40"/>
     </row>
     <row r="47" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="41"/>
       <c r="B47" s="35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C47" s="47">
-        <v>43173</v>
+        <v>43181</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E47" s="38">
-        <v>8010601051334</v>
+        <v>1010401135178</v>
       </c>
       <c r="F47" s="43" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="G47" s="42" t="s">
-        <v>339</v>
+        <v>170</v>
       </c>
       <c r="H47" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I47" s="39"/>
       <c r="J47" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K47" s="40"/>
     </row>
     <row r="48" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="41"/>
       <c r="B48" s="35" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C48" s="47">
-        <v>43181</v>
+        <v>43213</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>290</v>
+        <v>172</v>
       </c>
       <c r="E48" s="38">
-        <v>1010401135178</v>
+        <v>1010001188907</v>
       </c>
       <c r="F48" s="43" t="s">
-        <v>363</v>
+        <v>141</v>
       </c>
       <c r="G48" s="42" t="s">
         <v>173</v>
@@ -6674,239 +6628,239 @@
       </c>
       <c r="I48" s="39"/>
       <c r="J48" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K48" s="40"/>
     </row>
     <row r="49" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="41"/>
       <c r="B49" s="35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C49" s="47">
-        <v>43213</v>
+        <v>43263</v>
       </c>
       <c r="D49" s="42" t="s">
-        <v>175</v>
+        <v>384</v>
       </c>
       <c r="E49" s="38">
-        <v>1010001188907</v>
+        <v>3010001183897</v>
       </c>
       <c r="F49" s="43" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="H49" s="43" t="s">
-        <v>177</v>
+        <v>413</v>
       </c>
       <c r="I49" s="39"/>
       <c r="J49" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K49" s="40"/>
     </row>
     <row r="50" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="41"/>
       <c r="B50" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C50" s="47">
-        <v>43263</v>
+        <v>43307</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>389</v>
+        <v>287</v>
       </c>
       <c r="E50" s="38">
-        <v>3010001183897</v>
+        <v>8010001188396</v>
       </c>
       <c r="F50" s="43" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="G50" s="42" t="s">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="H50" s="43" t="s">
-        <v>418</v>
+        <v>176</v>
       </c>
       <c r="I50" s="39"/>
       <c r="J50" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K50" s="40"/>
     </row>
     <row r="51" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="41"/>
       <c r="B51" s="35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C51" s="47">
-        <v>43307</v>
+        <v>43308</v>
       </c>
       <c r="D51" s="42" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E51" s="38">
-        <v>8010001188396</v>
+        <v>5011401019978</v>
       </c>
       <c r="F51" s="43" t="s">
-        <v>178</v>
+        <v>376</v>
       </c>
       <c r="G51" s="42" t="s">
-        <v>238</v>
+        <v>380</v>
       </c>
       <c r="H51" s="43" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="I51" s="39"/>
       <c r="J51" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K51" s="40"/>
     </row>
     <row r="52" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="41"/>
       <c r="B52" s="35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C52" s="47">
-        <v>43308</v>
+        <v>43327</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E52" s="38">
-        <v>5011401019978</v>
+        <v>4010701034738</v>
       </c>
       <c r="F52" s="43" t="s">
-        <v>381</v>
+        <v>177</v>
       </c>
       <c r="G52" s="42" t="s">
-        <v>385</v>
+        <v>77</v>
       </c>
       <c r="H52" s="43" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="I52" s="39"/>
       <c r="J52" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K52" s="40"/>
     </row>
     <row r="53" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="41"/>
       <c r="B53" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="47">
+        <v>43375</v>
+      </c>
+      <c r="D53" s="42" t="s">
+        <v>290</v>
+      </c>
+      <c r="E53" s="48">
+        <v>4011001117670</v>
+      </c>
+      <c r="F53" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="G53" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="47">
-        <v>43327</v>
-      </c>
-      <c r="D53" s="42" t="s">
-        <v>293</v>
-      </c>
-      <c r="E53" s="38">
-        <v>4010701034738</v>
-      </c>
-      <c r="F53" s="43" t="s">
+      <c r="H53" s="43" t="s">
         <v>180</v>
-      </c>
-      <c r="G53" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="H53" s="43" t="s">
-        <v>181</v>
       </c>
       <c r="I53" s="39"/>
       <c r="J53" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K53" s="40"/>
     </row>
     <row r="54" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="41"/>
       <c r="B54" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="47">
-        <v>43375</v>
+        <v>97</v>
+      </c>
+      <c r="C54" s="47" t="s">
+        <v>98</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E54" s="48">
-        <v>4011001117670</v>
+        <v>3013301041741</v>
       </c>
       <c r="F54" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="G54" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="H54" s="43" t="s">
         <v>182</v>
-      </c>
-      <c r="G54" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="H54" s="43" t="s">
-        <v>183</v>
       </c>
       <c r="I54" s="39"/>
       <c r="J54" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K54" s="40"/>
     </row>
     <row r="55" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="41"/>
       <c r="B55" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="C55" s="47" t="s">
-        <v>101</v>
-      </c>
       <c r="D55" s="42" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E55" s="48">
-        <v>3013301041741</v>
+        <v>3010901038102</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="G55" s="42" t="s">
-        <v>375</v>
+        <v>251</v>
       </c>
       <c r="H55" s="43" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I55" s="39"/>
       <c r="J55" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K55" s="40"/>
     </row>
     <row r="56" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="41"/>
       <c r="B56" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="47" t="s">
+      <c r="D56" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="E56" s="48">
+        <v>5010001192707</v>
+      </c>
+      <c r="F56" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="G56" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="D56" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="E56" s="48">
-        <v>3010901038102</v>
-      </c>
-      <c r="F56" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="G56" s="42" t="s">
-        <v>254</v>
-      </c>
       <c r="H56" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I56" s="39"/>
       <c r="J56" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K56" s="40"/>
     </row>
@@ -6919,81 +6873,81 @@
         <v>105</v>
       </c>
       <c r="D57" s="42" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E57" s="48">
-        <v>5010001192707</v>
+        <v>7013301041449</v>
       </c>
       <c r="F57" s="43" t="s">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="G57" s="42" t="s">
-        <v>106</v>
+        <v>240</v>
       </c>
       <c r="H57" s="43" t="s">
-        <v>187</v>
+        <v>241</v>
       </c>
       <c r="I57" s="39"/>
       <c r="J57" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K57" s="40"/>
     </row>
     <row r="58" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
       <c r="B58" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="C58" s="47" t="s">
-        <v>108</v>
-      </c>
       <c r="D58" s="42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E58" s="48">
-        <v>7013301041449</v>
+        <v>3010001167611</v>
       </c>
       <c r="F58" s="43" t="s">
-        <v>242</v>
+        <v>341</v>
       </c>
       <c r="G58" s="42" t="s">
-        <v>243</v>
+        <v>342</v>
       </c>
       <c r="H58" s="43" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="I58" s="39"/>
       <c r="J58" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K58" s="40"/>
     </row>
     <row r="59" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="41"/>
       <c r="B59" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="47" t="s">
+      <c r="D59" s="42" t="s">
+        <v>296</v>
+      </c>
+      <c r="E59" s="48">
+        <v>3010401049814</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="G59" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="D59" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="E59" s="48">
-        <v>3010001167611</v>
-      </c>
-      <c r="F59" s="43" t="s">
-        <v>346</v>
-      </c>
-      <c r="G59" s="42" t="s">
-        <v>347</v>
-      </c>
       <c r="H59" s="43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I59" s="39"/>
       <c r="J59" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K59" s="40"/>
     </row>
@@ -7006,257 +6960,257 @@
         <v>112</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E60" s="48">
-        <v>3010401049814</v>
+        <v>2010001190192</v>
       </c>
       <c r="F60" s="43" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="G60" s="42" t="s">
-        <v>113</v>
+        <v>387</v>
       </c>
       <c r="H60" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="I60" s="39"/>
+        <v>209</v>
+      </c>
+      <c r="I60" s="39" t="s">
+        <v>200</v>
+      </c>
       <c r="J60" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K60" s="40"/>
     </row>
     <row r="61" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="41"/>
       <c r="B61" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C61" s="47" t="s">
         <v>115</v>
       </c>
+      <c r="C61" s="47">
+        <v>43868</v>
+      </c>
       <c r="D61" s="42" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E61" s="48">
-        <v>2010001190192</v>
+        <v>5011801019594</v>
       </c>
       <c r="F61" s="43" t="s">
-        <v>211</v>
+        <v>389</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="H61" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="I61" s="39" t="s">
-        <v>203</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="I61" s="39"/>
       <c r="J61" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K61" s="40"/>
     </row>
     <row r="62" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="41"/>
       <c r="B62" s="35" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C62" s="47">
         <v>43868</v>
       </c>
       <c r="D62" s="42" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E62" s="48">
-        <v>5011801019594</v>
+        <v>3010001161300</v>
       </c>
       <c r="F62" s="43" t="s">
-        <v>394</v>
+        <v>34</v>
       </c>
       <c r="G62" s="42" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="H62" s="43" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="I62" s="39"/>
       <c r="J62" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K62" s="40"/>
     </row>
     <row r="63" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="41"/>
       <c r="B63" s="35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C63" s="47">
-        <v>43868</v>
+        <v>43887</v>
       </c>
       <c r="D63" s="42" t="s">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="E63" s="48">
-        <v>3010001161300</v>
+        <v>9011401020230</v>
       </c>
       <c r="F63" s="43" t="s">
-        <v>36</v>
+        <v>337</v>
       </c>
       <c r="G63" s="42" t="s">
-        <v>419</v>
+        <v>338</v>
       </c>
       <c r="H63" s="43" t="s">
-        <v>406</v>
+        <v>188</v>
       </c>
       <c r="I63" s="39"/>
       <c r="J63" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K63" s="40"/>
     </row>
     <row r="64" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="41"/>
       <c r="B64" s="35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C64" s="47">
-        <v>43887</v>
+        <v>43888</v>
       </c>
       <c r="D64" s="42" t="s">
-        <v>386</v>
+        <v>313</v>
       </c>
       <c r="E64" s="48">
-        <v>9011401020230</v>
+        <v>9010401134148</v>
       </c>
       <c r="F64" s="43" t="s">
-        <v>342</v>
+        <v>154</v>
       </c>
       <c r="G64" s="42" t="s">
-        <v>343</v>
+        <v>250</v>
       </c>
       <c r="H64" s="43" t="s">
-        <v>191</v>
+        <v>423</v>
       </c>
       <c r="I64" s="39"/>
       <c r="J64" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K64" s="40"/>
     </row>
     <row r="65" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="41"/>
       <c r="B65" s="35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C65" s="47">
-        <v>43888</v>
+        <v>43899</v>
       </c>
       <c r="D65" s="42" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="E65" s="48">
-        <v>9010401134148</v>
+        <v>7040001086061</v>
       </c>
       <c r="F65" s="43" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="G65" s="42" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="H65" s="43" t="s">
-        <v>428</v>
+        <v>243</v>
       </c>
       <c r="I65" s="39"/>
       <c r="J65" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K65" s="40"/>
     </row>
     <row r="66" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="41"/>
       <c r="B66" s="35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C66" s="47">
-        <v>43899</v>
+        <v>43922</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="E66" s="48">
-        <v>7040001086061</v>
+        <v>6020001125152</v>
       </c>
       <c r="F66" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="G66" s="42" t="s">
-        <v>245</v>
+        <v>189</v>
+      </c>
+      <c r="G66" s="37" t="s">
+        <v>343</v>
       </c>
       <c r="H66" s="43" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="I66" s="39"/>
       <c r="J66" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K66" s="40"/>
     </row>
     <row r="67" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="41"/>
       <c r="B67" s="35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C67" s="47">
-        <v>43922</v>
+        <v>44056</v>
       </c>
       <c r="D67" s="42" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E67" s="48">
-        <v>6020001125152</v>
+        <v>7010001206332</v>
       </c>
       <c r="F67" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="G67" s="37" t="s">
-        <v>348</v>
+        <v>236</v>
+      </c>
+      <c r="G67" s="42" t="s">
+        <v>237</v>
       </c>
       <c r="H67" s="43" t="s">
-        <v>344</v>
+        <v>238</v>
       </c>
       <c r="I67" s="39"/>
       <c r="J67" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K67" s="40"/>
     </row>
     <row r="68" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="41"/>
       <c r="B68" s="35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C68" s="47">
-        <v>44056</v>
+        <v>44070</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E68" s="48">
-        <v>7010001206332</v>
+        <v>9011001103831</v>
       </c>
       <c r="F68" s="43" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G68" s="42" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="H68" s="43" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="I68" s="39"/>
       <c r="J68" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K68" s="40"/>
     </row>
@@ -7266,80 +7220,80 @@
         <v>125</v>
       </c>
       <c r="C69" s="47">
-        <v>44070</v>
+        <v>44127</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E69" s="48">
-        <v>9011001103831</v>
+        <v>8011001127534</v>
       </c>
       <c r="F69" s="43" t="s">
-        <v>248</v>
+        <v>341</v>
       </c>
       <c r="G69" s="42" t="s">
-        <v>249</v>
+        <v>363</v>
       </c>
       <c r="H69" s="43" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="I69" s="39"/>
       <c r="J69" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K69" s="40"/>
     </row>
     <row r="70" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="41"/>
       <c r="B70" s="35" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="C70" s="47">
-        <v>44127</v>
+        <v>44335</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E70" s="48">
-        <v>8011001127534</v>
+        <v>6013201011825</v>
       </c>
       <c r="F70" s="43" t="s">
-        <v>346</v>
+        <v>197</v>
       </c>
       <c r="G70" s="42" t="s">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="H70" s="43" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="I70" s="39"/>
       <c r="J70" s="39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K70" s="40"/>
     </row>
     <row r="71" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="41"/>
       <c r="B71" s="35" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C71" s="47">
-        <v>44335</v>
+        <v>44371</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E71" s="48">
-        <v>6013201011825</v>
+        <v>8010401050511</v>
       </c>
       <c r="F71" s="43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G71" s="42" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="H71" s="43" t="s">
-        <v>202</v>
+        <v>398</v>
       </c>
       <c r="I71" s="39"/>
       <c r="J71" s="39" t="s">
@@ -7350,605 +7304,576 @@
     <row r="72" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
       <c r="B72" s="35" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C72" s="47">
-        <v>44371</v>
+        <v>44403</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E72" s="48">
-        <v>8010401050511</v>
+        <v>5010401134795</v>
       </c>
       <c r="F72" s="43" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H72" s="43" t="s">
-        <v>403</v>
+        <v>207</v>
       </c>
       <c r="I72" s="39"/>
       <c r="J72" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K72" s="40"/>
     </row>
     <row r="73" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="41"/>
       <c r="B73" s="35" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C73" s="47">
-        <v>44403</v>
+        <v>44650</v>
       </c>
       <c r="D73" s="42" t="s">
-        <v>310</v>
+        <v>219</v>
       </c>
       <c r="E73" s="48">
-        <v>5010401134795</v>
+        <v>5012401017708</v>
       </c>
       <c r="F73" s="43" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="G73" s="42" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H73" s="43" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="I73" s="39"/>
       <c r="J73" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K73" s="40"/>
     </row>
     <row r="74" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="41"/>
       <c r="B74" s="35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C74" s="47">
         <v>44650</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="E74" s="48">
-        <v>5012401017708</v>
+        <v>2040001094812</v>
       </c>
       <c r="F74" s="43" t="s">
-        <v>223</v>
+        <v>135</v>
       </c>
       <c r="G74" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="H74" s="43" t="s">
         <v>224</v>
-      </c>
-      <c r="H74" s="43" t="s">
-        <v>225</v>
       </c>
       <c r="I74" s="39"/>
       <c r="J74" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K74" s="40"/>
     </row>
     <row r="75" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="41"/>
       <c r="B75" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C75" s="47">
         <v>44650</v>
       </c>
       <c r="D75" s="42" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E75" s="48">
-        <v>2040001094812</v>
+        <v>8013301009057</v>
       </c>
       <c r="F75" s="43" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="G75" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H75" s="43" t="s">
         <v>227</v>
       </c>
       <c r="I75" s="39"/>
       <c r="J75" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K75" s="40"/>
     </row>
     <row r="76" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="41"/>
       <c r="B76" s="35" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="C76" s="47">
-        <v>44650</v>
+        <v>44978</v>
       </c>
       <c r="D76" s="42" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E76" s="48">
-        <v>8013301009057</v>
+        <v>4010401049813</v>
       </c>
       <c r="F76" s="43" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
       <c r="G76" s="42" t="s">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="H76" s="43" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="I76" s="39"/>
       <c r="J76" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K76" s="40"/>
     </row>
     <row r="77" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="41"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="35" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="C77" s="47">
-        <v>44978</v>
+        <v>45254</v>
       </c>
       <c r="D77" s="42" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E77" s="48">
-        <v>4010401049813</v>
+        <v>3010401113537</v>
       </c>
       <c r="F77" s="43" t="s">
-        <v>39</v>
+        <v>181</v>
       </c>
       <c r="G77" s="42" t="s">
-        <v>23</v>
+        <v>326</v>
       </c>
       <c r="H77" s="43" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="I77" s="39"/>
       <c r="J77" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K77" s="40"/>
     </row>
     <row r="78" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="49"/>
       <c r="B78" s="35" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C78" s="47">
-        <v>45254</v>
+        <v>45275</v>
       </c>
       <c r="D78" s="42" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="E78" s="48">
-        <v>3010401113537</v>
+        <v>6011101086450</v>
       </c>
       <c r="F78" s="43" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="G78" s="42" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="H78" s="43" t="s">
-        <v>323</v>
+        <v>415</v>
       </c>
       <c r="I78" s="39"/>
       <c r="J78" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K78" s="40"/>
     </row>
     <row r="79" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="49"/>
       <c r="B79" s="35" t="s">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="C79" s="47">
-        <v>45275</v>
+        <v>45735</v>
       </c>
       <c r="D79" s="42" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="E79" s="48">
-        <v>6011101086450</v>
+        <v>9010001141627</v>
       </c>
       <c r="F79" s="43" t="s">
-        <v>146</v>
+        <v>360</v>
       </c>
       <c r="G79" s="42" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="H79" s="43" t="s">
-        <v>420</v>
+        <v>362</v>
       </c>
       <c r="I79" s="39"/>
       <c r="J79" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="K79" s="40"/>
+        <v>203</v>
+      </c>
+      <c r="K79" s="39"/>
     </row>
     <row r="80" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="49"/>
       <c r="B80" s="35" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C80" s="47">
-        <v>45735</v>
+        <v>45887</v>
       </c>
       <c r="D80" s="42" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E80" s="48">
-        <v>9010001141627</v>
+        <v>1010001205562</v>
       </c>
       <c r="F80" s="43" t="s">
-        <v>365</v>
+        <v>154</v>
       </c>
       <c r="G80" s="42" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="H80" s="43" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="I80" s="39"/>
       <c r="J80" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="K80" s="39"/>
+        <v>203</v>
+      </c>
+      <c r="K80" s="40"/>
     </row>
     <row r="81" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="49"/>
-      <c r="B81" s="35" t="s">
+      <c r="B81" s="50" t="s">
         <v>377</v>
       </c>
-      <c r="C81" s="47">
-        <v>45887</v>
+      <c r="C81" s="51">
+        <v>45908</v>
       </c>
       <c r="D81" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="E81" s="52">
+        <v>1010401137711</v>
+      </c>
+      <c r="F81" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="G81" s="54" t="s">
+        <v>416</v>
+      </c>
+      <c r="H81" s="53" t="s">
         <v>379</v>
       </c>
-      <c r="E81" s="48">
-        <v>1010001205562</v>
-      </c>
-      <c r="F81" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="G81" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="H81" s="43" t="s">
-        <v>380</v>
-      </c>
-      <c r="I81" s="39"/>
-      <c r="J81" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="K81" s="40"/>
+      <c r="I81" s="55"/>
+      <c r="J81" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="K81" s="56"/>
     </row>
     <row r="82" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="49"/>
       <c r="B82" s="50" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C82" s="51">
-        <v>45908</v>
+        <v>46132</v>
       </c>
       <c r="D82" s="42" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E82" s="52">
-        <v>1010401137711</v>
+        <v>9010001256136</v>
       </c>
       <c r="F82" s="53" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="G82" s="54" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="H82" s="53" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="I82" s="55"/>
       <c r="J82" s="55" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K82" s="56"/>
     </row>
     <row r="83" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="49"/>
       <c r="B83" s="50" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C83" s="51">
-        <v>46132</v>
+        <v>46178</v>
       </c>
       <c r="D83" s="42" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="E83" s="52">
-        <v>9010001256136</v>
+        <v>9011101027550</v>
       </c>
       <c r="F83" s="53" t="s">
-        <v>20</v>
+        <v>405</v>
       </c>
       <c r="G83" s="54" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H83" s="53" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="I83" s="55"/>
       <c r="J83" s="55" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K83" s="56"/>
     </row>
-    <row r="84" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="49"/>
-      <c r="B84" s="50" t="s">
-        <v>408</v>
-      </c>
-      <c r="C84" s="51">
-        <v>46178</v>
+    <row r="84" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="57"/>
+      <c r="B84" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="C84" s="58">
+        <v>46251</v>
       </c>
       <c r="D84" s="42" t="s">
-        <v>409</v>
-      </c>
-      <c r="E84" s="52">
-        <v>9011101027550</v>
-      </c>
-      <c r="F84" s="53" t="s">
-        <v>410</v>
-      </c>
-      <c r="G84" s="54" t="s">
-        <v>407</v>
-      </c>
-      <c r="H84" s="53" t="s">
-        <v>411</v>
-      </c>
-      <c r="I84" s="55"/>
-      <c r="J84" s="55" t="s">
-        <v>203</v>
-      </c>
-      <c r="K84" s="56"/>
+        <v>419</v>
+      </c>
+      <c r="E84" s="59">
+        <v>6010001125005</v>
+      </c>
+      <c r="F84" s="60" t="s">
+        <v>420</v>
+      </c>
+      <c r="G84" s="61" t="s">
+        <v>421</v>
+      </c>
+      <c r="H84" s="60" t="s">
+        <v>422</v>
+      </c>
+      <c r="I84" s="25"/>
+      <c r="J84" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="K84" s="26"/>
     </row>
     <row r="85" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="80"/>
-      <c r="B85" s="21" t="s">
-        <v>423</v>
-      </c>
-      <c r="C85" s="81">
-        <v>46251</v>
-      </c>
-      <c r="D85" s="42" t="s">
-        <v>424</v>
-      </c>
-      <c r="E85" s="82">
-        <v>6010001125005</v>
-      </c>
-      <c r="F85" s="83" t="s">
-        <v>425</v>
-      </c>
-      <c r="G85" s="57" t="s">
-        <v>426</v>
-      </c>
-      <c r="H85" s="83" t="s">
-        <v>427</v>
-      </c>
-      <c r="I85" s="25"/>
-      <c r="J85" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="K85" s="26"/>
-    </row>
-    <row r="86" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="34" t="str">
-        <f>"東海財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"東海財務局*")&amp;"業者】"</f>
+      <c r="A85" s="34" t="str">
+        <f>"東海財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"東海財務局*")&amp;"業者】"</f>
         <v>東海財務局
 【計1業者】</v>
       </c>
-      <c r="B86" s="58" t="s">
+      <c r="B85" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" s="63">
+        <v>40575</v>
+      </c>
+      <c r="D85" s="64" t="s">
+        <v>310</v>
+      </c>
+      <c r="E85" s="65">
+        <v>5200001003514</v>
+      </c>
+      <c r="F85" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="H85" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="C86" s="59">
-        <v>40575</v>
-      </c>
-      <c r="D86" s="60" t="s">
-        <v>314</v>
-      </c>
-      <c r="E86" s="61">
-        <v>5200001003514</v>
-      </c>
-      <c r="F86" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="G86" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="H86" s="58" t="s">
-        <v>90</v>
-      </c>
-      <c r="I86" s="62"/>
-      <c r="J86" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="K86" s="63"/>
-    </row>
-    <row r="87" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="27" t="str">
-        <f>"北陸財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$861,"北陸財務局*")&amp;"業者】"</f>
+      <c r="I85" s="66"/>
+      <c r="J85" s="66" t="s">
+        <v>200</v>
+      </c>
+      <c r="K85" s="67"/>
+    </row>
+    <row r="86" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="27" t="str">
+        <f>"北陸財務局"&amp;CHAR(10)&amp;"【計"&amp;COUNTIF($B$5:$B$860,"北陸財務局*")&amp;"業者】"</f>
         <v>北陸財務局
 【計1業者】</v>
       </c>
-      <c r="B87" s="64" t="s">
+      <c r="B86" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C86" s="69">
+        <v>41075</v>
+      </c>
+      <c r="D86" s="70" t="s">
+        <v>311</v>
+      </c>
+      <c r="E86" s="71">
+        <v>3210001014413</v>
+      </c>
+      <c r="F86" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="G86" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="H86" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="C87" s="65">
-        <v>41075</v>
-      </c>
-      <c r="D87" s="66" t="s">
-        <v>315</v>
-      </c>
-      <c r="E87" s="67">
-        <v>3210001014413</v>
-      </c>
-      <c r="F87" s="64" t="s">
+      <c r="I86" s="66"/>
+      <c r="J86" s="66" t="s">
+        <v>195</v>
+      </c>
+      <c r="K86" s="72"/>
+    </row>
+    <row r="87" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="73" t="s">
+        <v>347</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="29">
+        <v>42174</v>
+      </c>
+      <c r="D87" s="74" t="s">
+        <v>312</v>
+      </c>
+      <c r="E87" s="31">
+        <v>2120001137521</v>
+      </c>
+      <c r="F87" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="G87" s="66" t="s">
+      <c r="G87" s="74" t="s">
+        <v>95</v>
+      </c>
+      <c r="H87" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="H87" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="I87" s="62"/>
-      <c r="J87" s="62" t="s">
-        <v>198</v>
-      </c>
-      <c r="K87" s="68"/>
+      <c r="I87" s="32"/>
+      <c r="J87" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="K87" s="76"/>
     </row>
     <row r="88" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="69" t="s">
+      <c r="A88" s="34"/>
+      <c r="B88" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="C88" s="36">
+        <v>45673</v>
+      </c>
+      <c r="D88" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="E88" s="38">
+        <v>1120001059675</v>
+      </c>
+      <c r="F88" s="77" t="s">
+        <v>350</v>
+      </c>
+      <c r="G88" s="42" t="s">
+        <v>351</v>
+      </c>
+      <c r="H88" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="B88" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C88" s="29">
-        <v>42174</v>
-      </c>
-      <c r="D88" s="70" t="s">
-        <v>316</v>
-      </c>
-      <c r="E88" s="31">
-        <v>2120001137521</v>
-      </c>
-      <c r="F88" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="G88" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="H88" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="I88" s="32"/>
-      <c r="J88" s="32" t="s">
-        <v>198</v>
-      </c>
-      <c r="K88" s="72"/>
-    </row>
-    <row r="89" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="34"/>
-      <c r="B89" s="35" t="s">
+      <c r="I88" s="39"/>
+      <c r="J88" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K88" s="78"/>
+    </row>
+    <row r="89" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="20"/>
+      <c r="B89" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C89" s="36">
-        <v>45673</v>
-      </c>
-      <c r="D89" s="42" t="s">
+      <c r="C89" s="22">
+        <v>45688</v>
+      </c>
+      <c r="D89" s="61" t="s">
         <v>354</v>
       </c>
-      <c r="E89" s="38">
-        <v>1120001059675</v>
-      </c>
-      <c r="F89" s="73" t="s">
+      <c r="E89" s="24">
+        <v>9120001075640</v>
+      </c>
+      <c r="F89" s="79" t="s">
         <v>355</v>
       </c>
-      <c r="G89" s="42" t="s">
+      <c r="G89" s="61" t="s">
         <v>356</v>
       </c>
-      <c r="H89" s="35" t="s">
+      <c r="H89" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="I89" s="39"/>
-      <c r="J89" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="K89" s="74"/>
-    </row>
-    <row r="90" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="20"/>
-      <c r="B90" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="C90" s="22">
-        <v>45688</v>
-      </c>
-      <c r="D90" s="57" t="s">
-        <v>359</v>
-      </c>
-      <c r="E90" s="24">
-        <v>9120001075640</v>
-      </c>
-      <c r="F90" s="75" t="s">
-        <v>360</v>
-      </c>
-      <c r="G90" s="57" t="s">
-        <v>361</v>
-      </c>
-      <c r="H90" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="I90" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="J90" s="25"/>
-      <c r="K90" s="76"/>
+      <c r="I89" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="J89" s="25"/>
+      <c r="K89" s="80"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" s="81" t="s">
+        <v>216</v>
+      </c>
+      <c r="B90" s="81"/>
+      <c r="C90" s="81"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="81"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="81"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="77" t="s">
-        <v>219</v>
-      </c>
-      <c r="B91" s="77"/>
-      <c r="C91" s="77"/>
-      <c r="D91" s="78"/>
-      <c r="E91" s="78"/>
-      <c r="F91" s="77"/>
-      <c r="G91" s="78"/>
-      <c r="H91" s="77"/>
+      <c r="A91" s="81"/>
+      <c r="B91" s="81"/>
+      <c r="C91" s="81"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="81"/>
+      <c r="G91" s="82"/>
+      <c r="H91" s="81"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="77"/>
-      <c r="B92" s="77"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="78"/>
-      <c r="E92" s="78"/>
-      <c r="F92" s="77"/>
-      <c r="G92" s="78"/>
-      <c r="H92" s="77"/>
+      <c r="A92" s="81"/>
+      <c r="B92" s="81"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="82"/>
+      <c r="E92" s="82"/>
+      <c r="F92" s="81"/>
+      <c r="G92" s="82"/>
+      <c r="H92" s="81"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="77"/>
-      <c r="B93" s="77"/>
-      <c r="C93" s="77"/>
-      <c r="D93" s="78"/>
-      <c r="E93" s="78"/>
-      <c r="F93" s="77"/>
-      <c r="G93" s="78"/>
-      <c r="H93" s="77"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="77"/>
-      <c r="B94" s="77"/>
-      <c r="C94" s="77"/>
-      <c r="D94" s="78"/>
-      <c r="E94" s="78"/>
-      <c r="F94" s="77"/>
-      <c r="G94" s="78"/>
-      <c r="H94" s="77"/>
+      <c r="A93" s="81"/>
+      <c r="B93" s="81"/>
+      <c r="C93" s="81"/>
+      <c r="D93" s="82"/>
+      <c r="E93" s="82"/>
+      <c r="F93" s="81"/>
+      <c r="G93" s="82"/>
+      <c r="H93" s="81"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:K5" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -7971,17 +7896,276 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
-    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A86:A87" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A85:A86" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="35" max="10" man="1"/>
-    <brk id="50" max="10" man="1"/>
-    <brk id="65" max="10" man="1"/>
-    <brk id="81" max="10" man="1"/>
+    <brk id="34" max="10" man="1"/>
+    <brk id="49" max="10" man="1"/>
+    <brk id="64" max="10" man="1"/>
+    <brk id="79" max="10" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="32c3a57c-5296-4003-b936-9ab25ad0923d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100983B318F74802D4ABEFADEC269058BE9" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="1908bdf7e2a759c5d3bec18ce44fe038">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="32c3a57c-5296-4003-b936-9ab25ad0923d" xmlns:ns3="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3877253f6ba9ebfbd06dda58d5ecc6dc" ns2:_="" ns3:_="">
+    <xsd:import namespace="32c3a57c-5296-4003-b936-9ab25ad0923d"/>
+    <xsd:import namespace="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="32c3a57c-5296-4003-b936-9ab25ad0923d" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1e1c6816-2a4f-4461-93c7-8dd281d6228d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c52ab56e-ac1a-462d-a023-20ac0a678e2a}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D37A222A-D56C-4197-A9D8-4E4C7A2E4328}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="32c3a57c-5296-4003-b936-9ab25ad0923d"/>
+    <ds:schemaRef ds:uri="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22F7B942-00C4-4CCA-9D47-F052EC154F5A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="32c3a57c-5296-4003-b936-9ab25ad0923d"/>
+    <ds:schemaRef ds:uri="9a90d419-12d7-4f50-a7cb-dd3ac3affbc4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7286210E-9387-43B0-B5AC-B2D6CC698180}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>